--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -803,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -845,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
@@ -857,7 +864,7 @@
         <v>200</v>
       </c>
       <c r="Y8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>200</v>
@@ -869,19 +876,25 @@
         <v>200</v>
       </c>
       <c r="AC8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AD8" s="3">
         <v>200</v>
       </c>
       <c r="AE8" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AF8" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -924,56 +937,62 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>200</v>
-      </c>
-      <c r="S9" s="3">
-        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>200</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X9" s="3">
         <v>200</v>
       </c>
       <c r="Y9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Z9" s="3">
-        <v>300</v>
-      </c>
       <c r="AA9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB9" s="3">
         <v>300</v>
       </c>
       <c r="AC9" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AD9" s="3">
         <v>300</v>
       </c>
       <c r="AE9" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG9" s="3">
         <v>1200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1016,14 +1035,14 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>-200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>-100</v>
       </c>
       <c r="T10" s="3">
         <v>-200</v>
@@ -1032,10 +1051,10 @@
         <v>-100</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>
@@ -1044,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="Z10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="3">
         <v>-100</v>
@@ -1059,13 +1078,19 @@
         <v>-100</v>
       </c>
       <c r="AE10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG10" s="3">
         <v>-400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1314,11 +1353,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1332,50 +1371,56 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-900</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1548,10 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1554,43 +1607,49 @@
         <v>100</v>
       </c>
       <c r="U17" s="3">
+        <v>100</v>
+      </c>
+      <c r="V17" s="3">
+        <v>100</v>
+      </c>
+      <c r="W17" s="3">
         <v>300</v>
-      </c>
-      <c r="V17" s="3">
-        <v>300</v>
-      </c>
-      <c r="W17" s="3">
-        <v>200</v>
       </c>
       <c r="X17" s="3">
         <v>300</v>
       </c>
       <c r="Y17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1604,16 +1663,16 @@
         <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
@@ -1646,14 +1705,14 @@
         <v>-100</v>
       </c>
       <c r="U18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-100</v>
-      </c>
       <c r="X18" s="3">
         <v>-100</v>
       </c>
@@ -1661,28 +1720,34 @@
         <v>-100</v>
       </c>
       <c r="Z18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>200</v>
       </c>
-      <c r="AF18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1730,31 +1797,31 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
@@ -1763,7 +1830,7 @@
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
@@ -1772,43 +1839,49 @@
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
-        <v>100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1828,79 +1901,85 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="K21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="N21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3">
         <v>100</v>
       </c>
       <c r="Q21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T21" s="3">
         <v>0</v>
       </c>
       <c r="U21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>200</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD21" s="3">
         <v>0</v>
       </c>
       <c r="AE21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
         <v>700</v>
       </c>
-      <c r="AF21" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1913,11 +1992,11 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1991,8 +2070,14 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2012,13 +2097,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
@@ -2027,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
@@ -2036,55 +2121,61 @@
         <v>100</v>
       </c>
       <c r="Q23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>0</v>
       </c>
       <c r="AF23" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2364,14 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2288,13 +2391,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -2303,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
@@ -2312,55 +2415,61 @@
         <v>100</v>
       </c>
       <c r="Q26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
       <c r="U26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>0</v>
       </c>
       <c r="AF26" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2380,13 +2489,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -2395,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
         <v>0</v>
@@ -2404,55 +2513,61 @@
         <v>100</v>
       </c>
       <c r="Q27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>0</v>
       </c>
       <c r="AF27" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,37 +2658,43 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2585,31 +2706,31 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>2100</v>
       </c>
-      <c r="Q29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R29" s="3">
-        <v>-100</v>
-      </c>
       <c r="S29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-2300</v>
       </c>
-      <c r="U29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2834,31 +2973,31 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
@@ -2867,7 +3006,7 @@
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
@@ -2876,43 +3015,49 @@
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2932,13 +3077,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -2947,64 +3092,70 @@
         <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-100</v>
-      </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
-        <v>100</v>
-      </c>
       <c r="W33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>0</v>
       </c>
       <c r="AF33" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3246,14 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3116,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -3131,161 +3288,173 @@
         <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-100</v>
-      </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
-        <v>100</v>
-      </c>
       <c r="W35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>0</v>
       </c>
       <c r="AF35" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,19 +3523,21 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
       </c>
       <c r="F41" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G41" s="3">
         <v>400</v>
@@ -3376,22 +3549,22 @@
         <v>400</v>
       </c>
       <c r="J41" s="3">
+        <v>400</v>
+      </c>
+      <c r="K41" s="3">
+        <v>400</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>200</v>
       </c>
       <c r="M41" s="3">
         <v>300</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O41" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
@@ -3409,25 +3582,25 @@
         <v>0</v>
       </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>400</v>
       </c>
       <c r="AB41" s="3">
         <v>400</v>
@@ -3436,16 +3609,22 @@
         <v>400</v>
       </c>
       <c r="AD41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AF41" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,19 +3715,25 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3500</v>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G43" s="3">
         <v>3500</v>
@@ -3560,16 +3745,16 @@
         <v>3500</v>
       </c>
       <c r="J43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="K43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="L43" s="3">
         <v>3600</v>
       </c>
       <c r="M43" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="N43" s="3">
         <v>3600</v>
@@ -3584,34 +3769,34 @@
         <v>3700</v>
       </c>
       <c r="R43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T43" s="3">
         <v>4000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4100</v>
-      </c>
-      <c r="T43" s="3">
-        <v>4200</v>
-      </c>
-      <c r="U43" s="3">
-        <v>4300</v>
       </c>
       <c r="V43" s="3">
         <v>4200</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>4300</v>
       </c>
       <c r="X43" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>100</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,25 +3911,31 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -3756,19 +3953,19 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
-        <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3783,37 +3980,43 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>4100</v>
       </c>
-      <c r="X45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
       </c>
       <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3821,10 +4024,10 @@
         <v>500</v>
       </c>
       <c r="E46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="F46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="G46" s="3">
         <v>4000</v>
@@ -3836,87 +4039,93 @@
         <v>4000</v>
       </c>
       <c r="J46" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="K46" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="L46" s="3">
         <v>3900</v>
       </c>
       <c r="M46" s="3">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="N46" s="3">
         <v>3900</v>
       </c>
       <c r="O46" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="P46" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="Q46" s="3">
         <v>3800</v>
       </c>
       <c r="R46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T46" s="3">
         <v>4100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4300</v>
-      </c>
-      <c r="U46" s="3">
-        <v>4500</v>
-      </c>
-      <c r="V46" s="3">
-        <v>4700</v>
       </c>
       <c r="W46" s="3">
         <v>4500</v>
       </c>
       <c r="X46" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>700</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>700</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>400</v>
       </c>
       <c r="AF46" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>3500</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3500</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -3930,11 +4139,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3996,8 +4205,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4029,10 +4244,10 @@
         <v>600</v>
       </c>
       <c r="M48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O48" s="3">
         <v>700</v>
@@ -4041,55 +4256,61 @@
         <v>700</v>
       </c>
       <c r="Q48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="R48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="S48" s="3">
         <v>1400</v>
       </c>
       <c r="T48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>3200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>6100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>6200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>6300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>6300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4397,16 +4636,16 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -4415,22 +4654,22 @@
         <v>200</v>
       </c>
       <c r="S52" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
       </c>
       <c r="U52" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
       </c>
       <c r="W52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y52" s="3">
         <v>300</v>
@@ -4451,13 +4690,19 @@
         <v>300</v>
       </c>
       <c r="AE52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG52" s="3">
         <v>400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,13 +4793,19 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="E54" s="3">
         <v>4600</v>
@@ -4566,82 +4817,88 @@
         <v>4600</v>
       </c>
       <c r="H54" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="I54" s="3">
         <v>4600</v>
       </c>
       <c r="J54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="K54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="L54" s="3">
         <v>4500</v>
       </c>
       <c r="M54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O54" s="3">
         <v>4800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>4600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6000</v>
-      </c>
-      <c r="U54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="V54" s="3">
-        <v>8100</v>
       </c>
       <c r="W54" s="3">
         <v>7900</v>
       </c>
       <c r="X54" s="3">
+        <v>8100</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Z54" s="3">
         <v>3800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>4200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>7100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>7300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>7200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4967,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4720,25 +4981,25 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -4753,55 +5014,61 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
-        <v>100</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
-      </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>500</v>
       </c>
       <c r="AC57" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AD57" s="3">
         <v>500</v>
       </c>
       <c r="AE57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4833,19 +5100,19 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4854,10 +5121,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>100</v>
@@ -4890,10 +5157,16 @@
         <v>100</v>
       </c>
       <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4922,10 +5195,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
@@ -4937,7 +5210,7 @@
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
@@ -4946,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -4964,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4979,13 +5252,19 @@
         <v>100</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5017,67 +5296,73 @@
         <v>100</v>
       </c>
       <c r="M60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O60" s="3">
         <v>200</v>
       </c>
       <c r="P60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R60" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>300</v>
       </c>
       <c r="T60" s="3">
+        <v>500</v>
+      </c>
+      <c r="U60" s="3">
+        <v>300</v>
+      </c>
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
-        <v>100</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>700</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>700</v>
       </c>
       <c r="AD60" s="3">
         <v>700</v>
       </c>
       <c r="AE60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG60" s="3">
         <v>400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5109,19 +5394,19 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>200</v>
@@ -5154,10 +5439,10 @@
         <v>200</v>
       </c>
       <c r="AB61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD61" s="3">
         <v>300</v>
@@ -5166,10 +5451,16 @@
         <v>300</v>
       </c>
       <c r="AF61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5213,19 +5504,19 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>2700</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2900</v>
       </c>
       <c r="T62" s="3">
         <v>2800</v>
       </c>
       <c r="U62" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="V62" s="3">
         <v>2800</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5845,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5569,67 +5884,73 @@
         <v>100</v>
       </c>
       <c r="M66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O66" s="3">
         <v>300</v>
       </c>
       <c r="P66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>300</v>
+      </c>
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3600</v>
-      </c>
-      <c r="U66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="V66" s="3">
-        <v>3200</v>
       </c>
       <c r="W66" s="3">
         <v>3100</v>
       </c>
       <c r="X66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3600</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>3700</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>3700</v>
       </c>
       <c r="AD66" s="3">
         <v>3700</v>
       </c>
       <c r="AE66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG66" s="3">
         <v>3500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,34 +6371,40 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="E72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="F72" s="3">
         <v>-59000</v>
       </c>
       <c r="G72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="H72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="I72" s="3">
         <v>-59100</v>
       </c>
       <c r="J72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="K72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="L72" s="3">
         <v>-59200</v>
@@ -6069,61 +6416,67 @@
         <v>-59200</v>
       </c>
       <c r="O72" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="P72" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-59300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-61500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-61300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-61200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-61200</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-58900</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-58700</v>
       </c>
       <c r="W72" s="3">
         <v>-58900</v>
       </c>
       <c r="X72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-58800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-58700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,8 +6763,14 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6419,79 +6790,85 @@
         <v>4600</v>
       </c>
       <c r="I76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K76" s="3">
         <v>4500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>4400</v>
       </c>
       <c r="L76" s="3">
         <v>4400</v>
       </c>
       <c r="M76" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="N76" s="3">
         <v>4400</v>
       </c>
       <c r="O76" s="3">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="P76" s="3">
         <v>4400</v>
       </c>
       <c r="Q76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="R76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S76" s="3">
         <v>2200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>3600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>3700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6959,117 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6700,13 +7089,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
@@ -6715,64 +7104,70 @@
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
       <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-100</v>
-      </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
-        <v>100</v>
-      </c>
       <c r="W81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Y81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>0</v>
       </c>
       <c r="AF81" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6847,13 +7244,13 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6868,10 +7265,10 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -6886,19 +7283,25 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>700</v>
       </c>
-      <c r="AF83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,13 +7784,19 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -7378,79 +7811,85 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="U89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>100</v>
-      </c>
       <c r="W89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AF89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7527,26 +7968,26 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="V91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
@@ -7557,11 +7998,11 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7570,13 +8011,19 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,77 +8212,83 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
-        <v>100</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
+      <c r="M94" s="3">
+        <v>100</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-4000</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7846,13 +8305,19 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>700</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,19 +8738,25 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -8283,26 +8774,26 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8316,37 +8807,43 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>4400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-700</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,13 +8934,19 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -8458,26 +8961,26 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -8491,42 +8994,48 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -816,13 +820,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -858,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>200</v>
@@ -882,19 +886,22 @@
         <v>200</v>
       </c>
       <c r="AE8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF8" s="3">
         <v>400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,17 +950,17 @@
       <c r="R9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S9" s="3">
-        <v>200</v>
+      <c r="S9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T9" s="3">
         <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>200</v>
@@ -962,16 +969,16 @@
         <v>200</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
         <v>200</v>
       </c>
       <c r="AB9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC9" s="3">
         <v>300</v>
@@ -980,19 +987,22 @@
         <v>300</v>
       </c>
       <c r="AE9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF9" s="3">
         <v>500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1041,23 +1051,23 @@
       <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S10" s="3">
-        <v>-200</v>
+      <c r="S10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T10" s="3">
         <v>-200</v>
       </c>
       <c r="U10" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="V10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W10" s="3">
         <v>-200</v>
       </c>
-      <c r="W10" s="3">
-        <v>-100</v>
-      </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y10" s="3">
         <v>0</v>
@@ -1069,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="3">
         <v>-100</v>
@@ -1084,13 +1094,16 @@
         <v>-100</v>
       </c>
       <c r="AG10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>-400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,8 +1379,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1377,23 +1397,23 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1401,26 +1421,29 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2600</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-900</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1613,43 +1640,46 @@
         <v>100</v>
       </c>
       <c r="W17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X17" s="3">
         <v>300</v>
       </c>
       <c r="Y17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z17" s="3">
         <v>200</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>300</v>
       </c>
       <c r="AA17" s="3">
         <v>300</v>
       </c>
       <c r="AB17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1669,13 +1699,13 @@
         <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
       </c>
       <c r="K18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>-100</v>
@@ -1711,11 +1741,11 @@
         <v>-100</v>
       </c>
       <c r="W18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y18" s="3">
         <v>-100</v>
       </c>
@@ -1726,28 +1756,31 @@
         <v>-100</v>
       </c>
       <c r="AB18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
-      <c r="AH18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1803,17 +1837,17 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
@@ -1821,20 +1855,20 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
@@ -1845,16 +1879,16 @@
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1863,25 +1897,28 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1907,34 +1944,34 @@
         <v>0</v>
       </c>
       <c r="K21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <v>100</v>
       </c>
       <c r="Q21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U21" s="3">
         <v>0</v>
@@ -1943,43 +1980,46 @@
         <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>200</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
         <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <v>-100</v>
       </c>
       <c r="AC21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
       <c r="AE21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3">
         <v>700</v>
       </c>
-      <c r="AH21" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1998,8 +2038,8 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -2076,8 +2116,11 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2103,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -2118,19 +2161,19 @@
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U23" s="3">
         <v>0</v>
@@ -2139,43 +2182,46 @@
         <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>100</v>
       </c>
       <c r="Y23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
         <v>-100</v>
       </c>
       <c r="AA23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,8 +2419,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2397,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -2412,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U26" s="3">
         <v>0</v>
@@ -2433,43 +2485,46 @@
         <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>100</v>
       </c>
       <c r="Y26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="3">
         <v>-100</v>
       </c>
       <c r="AA26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2495,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="K27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -2510,19 +2565,19 @@
         <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U27" s="3">
         <v>0</v>
@@ -2531,43 +2586,46 @@
         <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>100</v>
       </c>
       <c r="Y27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="3">
         <v>-100</v>
       </c>
       <c r="AA27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2690,14 +2751,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2712,28 +2773,28 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>2100</v>
       </c>
-      <c r="S29" s="3">
-        <v>-100</v>
-      </c>
       <c r="T29" s="3">
         <v>-100</v>
       </c>
       <c r="U29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-2300</v>
       </c>
-      <c r="W29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="X29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2979,17 +3049,17 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
@@ -2997,20 +3067,20 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
@@ -3021,16 +3091,16 @@
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -3039,25 +3109,28 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3083,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -3098,64 +3171,67 @@
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
-        <v>-100</v>
-      </c>
       <c r="T33" s="3">
         <v>-100</v>
       </c>
       <c r="U33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z33" s="3">
         <v>-100</v>
       </c>
       <c r="AA33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,8 +3328,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3279,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -3294,167 +3373,173 @@
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
-        <v>-100</v>
-      </c>
       <c r="T35" s="3">
         <v>-100</v>
       </c>
       <c r="U35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z35" s="3">
         <v>-100</v>
       </c>
       <c r="AA35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3537,10 +3624,10 @@
         <v>400</v>
       </c>
       <c r="F41" s="3">
+        <v>400</v>
+      </c>
+      <c r="G41" s="3">
         <v>500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>400</v>
       </c>
       <c r="H41" s="3">
         <v>400</v>
@@ -3555,20 +3642,20 @@
         <v>400</v>
       </c>
       <c r="L41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M41" s="3">
         <v>300</v>
       </c>
       <c r="N41" s="3">
+        <v>300</v>
+      </c>
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
@@ -3588,22 +3675,22 @@
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>400</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>300</v>
       </c>
       <c r="AA41" s="3">
         <v>300</v>
       </c>
       <c r="AB41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC41" s="3">
         <v>400</v>
@@ -3615,16 +3702,19 @@
         <v>400</v>
       </c>
       <c r="AF41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AG41" s="3">
-        <v>100</v>
-      </c>
       <c r="AH41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3735,8 +3828,8 @@
       <c r="F43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="3">
-        <v>3500</v>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H43" s="3">
         <v>3500</v>
@@ -3751,7 +3844,7 @@
         <v>3500</v>
       </c>
       <c r="L43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="M43" s="3">
         <v>3600</v>
@@ -3760,46 +3853,46 @@
         <v>3600</v>
       </c>
       <c r="O43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P43" s="3">
         <v>3700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4200</v>
       </c>
-      <c r="Y43" s="3">
-        <v>100</v>
-      </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
       <c r="AB43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="3">
         <v>100</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,16 +4013,19 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3935,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3959,16 +4058,16 @@
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>100</v>
-      </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3986,13 +4085,13 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>4100</v>
       </c>
-      <c r="Z45" s="3">
-        <v>100</v>
-      </c>
       <c r="AA45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -4001,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>100</v>
@@ -4010,13 +4109,16 @@
         <v>100</v>
       </c>
       <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4030,7 +4132,7 @@
         <v>500</v>
       </c>
       <c r="G46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="H46" s="3">
         <v>4000</v>
@@ -4045,22 +4147,22 @@
         <v>4000</v>
       </c>
       <c r="L46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M46" s="3">
         <v>3900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>3800</v>
       </c>
       <c r="R46" s="3">
         <v>3800</v>
@@ -4069,52 +4171,55 @@
         <v>3800</v>
       </c>
       <c r="T46" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="U46" s="3">
         <v>4100</v>
       </c>
       <c r="V46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W46" s="3">
         <v>4300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4500</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>400</v>
       </c>
       <c r="AA46" s="3">
         <v>400</v>
       </c>
       <c r="AB46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC46" s="3">
         <v>500</v>
       </c>
       <c r="AD46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE46" s="3">
         <v>600</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>700</v>
       </c>
       <c r="AF46" s="3">
         <v>700</v>
       </c>
       <c r="AG46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH46" s="3">
         <v>400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4127,8 +4232,8 @@
       <c r="F47" s="3">
         <v>3500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
+      <c r="G47" s="3">
+        <v>3500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4145,8 +4250,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4250,7 +4358,7 @@
         <v>600</v>
       </c>
       <c r="O48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P48" s="3">
         <v>700</v>
@@ -4262,7 +4370,7 @@
         <v>700</v>
       </c>
       <c r="S48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="T48" s="3">
         <v>1400</v>
@@ -4271,46 +4379,49 @@
         <v>1400</v>
       </c>
       <c r="V48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W48" s="3">
         <v>1500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>3100</v>
       </c>
       <c r="Y48" s="3">
         <v>3100</v>
       </c>
       <c r="Z48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>3300</v>
       </c>
       <c r="AB48" s="3">
         <v>3300</v>
       </c>
       <c r="AC48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD48" s="3">
         <v>3400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6200</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>6300</v>
       </c>
       <c r="AG48" s="3">
         <v>6300</v>
       </c>
       <c r="AH48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AI48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4642,13 +4762,13 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -4660,10 +4780,10 @@
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
         <v>1100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>200</v>
       </c>
       <c r="W52" s="3">
         <v>200</v>
@@ -4672,7 +4792,7 @@
         <v>200</v>
       </c>
       <c r="Y52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z52" s="3">
         <v>300</v>
@@ -4696,13 +4816,16 @@
         <v>300</v>
       </c>
       <c r="AG52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH52" s="3">
         <v>400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,8 +4922,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4811,16 +4937,16 @@
         <v>4600</v>
       </c>
       <c r="F54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G54" s="3">
         <v>4700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>4600</v>
       </c>
       <c r="J54" s="3">
         <v>4600</v>
@@ -4829,7 +4955,7 @@
         <v>4600</v>
       </c>
       <c r="L54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="M54" s="3">
         <v>4500</v>
@@ -4838,67 +4964,70 @@
         <v>4500</v>
       </c>
       <c r="O54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="P54" s="3">
         <v>4800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4700</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>4600</v>
       </c>
       <c r="R54" s="3">
         <v>4600</v>
       </c>
       <c r="S54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="T54" s="3">
         <v>5400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4987,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -4999,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5020,20 +5151,20 @@
         <v>0</v>
       </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
-        <v>100</v>
-      </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
@@ -5041,34 +5172,37 @@
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5106,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
@@ -5115,7 +5249,7 @@
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5127,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>100</v>
@@ -5163,10 +5297,13 @@
         <v>100</v>
       </c>
       <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5201,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
@@ -5216,13 +5353,13 @@
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -5243,19 +5380,19 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5302,7 +5442,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P60" s="3">
         <v>200</v>
@@ -5311,43 +5451,43 @@
         <v>200</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S60" s="3">
+        <v>100</v>
+      </c>
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
-        <v>100</v>
-      </c>
       <c r="X60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y60" s="3">
         <v>200</v>
       </c>
       <c r="Z60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AA60" s="3">
         <v>400</v>
       </c>
       <c r="AB60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>600</v>
       </c>
       <c r="AD60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AE60" s="3">
         <v>700</v>
@@ -5356,13 +5496,16 @@
         <v>700</v>
       </c>
       <c r="AG60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5400,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -5409,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>200</v>
@@ -5445,7 +5588,7 @@
         <v>200</v>
       </c>
       <c r="AD61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE61" s="3">
         <v>300</v>
@@ -5457,10 +5600,13 @@
         <v>300</v>
       </c>
       <c r="AH61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5510,16 +5656,16 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2900</v>
-      </c>
-      <c r="V62" s="3">
-        <v>2800</v>
       </c>
       <c r="W62" s="3">
         <v>2800</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5890,7 +6048,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P66" s="3">
         <v>300</v>
@@ -5899,43 +6057,43 @@
         <v>300</v>
       </c>
       <c r="R66" s="3">
+        <v>300</v>
+      </c>
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3200</v>
-      </c>
-      <c r="T66" s="3">
-        <v>3400</v>
       </c>
       <c r="U66" s="3">
         <v>3400</v>
       </c>
       <c r="V66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W66" s="3">
         <v>3600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3100</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>3400</v>
       </c>
       <c r="AA66" s="3">
         <v>3400</v>
       </c>
       <c r="AB66" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="AC66" s="3">
         <v>3600</v>
       </c>
       <c r="AD66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AE66" s="3">
         <v>3700</v>
@@ -5944,13 +6102,16 @@
         <v>3700</v>
       </c>
       <c r="AG66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AH66" s="3">
         <v>3500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6389,7 +6563,7 @@
         <v>-59100</v>
       </c>
       <c r="F72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="G72" s="3">
         <v>-59000</v>
@@ -6398,7 +6572,7 @@
         <v>-59000</v>
       </c>
       <c r="I72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="J72" s="3">
         <v>-59100</v>
@@ -6407,7 +6581,7 @@
         <v>-59100</v>
       </c>
       <c r="L72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="M72" s="3">
         <v>-59200</v>
@@ -6422,61 +6596,64 @@
         <v>-59200</v>
       </c>
       <c r="Q72" s="3">
-        <v>-59300</v>
+        <v>-59200</v>
       </c>
       <c r="R72" s="3">
         <v>-59300</v>
       </c>
       <c r="S72" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="T72" s="3">
         <v>-61500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-61300</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-61200</v>
       </c>
       <c r="V72" s="3">
         <v>-61200</v>
       </c>
       <c r="W72" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="X72" s="3">
         <v>-58900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-58700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-58900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,8 +6952,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6796,10 +6982,10 @@
         <v>4600</v>
       </c>
       <c r="K76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L76" s="3">
         <v>4500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>4400</v>
       </c>
       <c r="M76" s="3">
         <v>4400</v>
@@ -6808,67 +6994,70 @@
         <v>4400</v>
       </c>
       <c r="O76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P76" s="3">
         <v>4500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2300</v>
-      </c>
-      <c r="U76" s="3">
-        <v>2400</v>
       </c>
       <c r="V76" s="3">
         <v>2400</v>
       </c>
       <c r="W76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X76" s="3">
         <v>4700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>400</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>500</v>
       </c>
       <c r="AB76" s="3">
         <v>500</v>
       </c>
       <c r="AC76" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD76" s="3">
         <v>600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,111 +7154,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7095,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M81" s="3">
         <v>0</v>
@@ -7110,64 +7305,67 @@
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
-        <v>-100</v>
-      </c>
       <c r="T81" s="3">
         <v>-100</v>
       </c>
       <c r="U81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="Z81" s="3">
         <v>-100</v>
       </c>
       <c r="AA81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7250,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7271,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7289,19 +7488,22 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3">
-        <v>100</v>
-      </c>
       <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>700</v>
       </c>
-      <c r="AH83" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,16 +8004,19 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
@@ -7817,32 +8034,32 @@
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -7850,46 +8067,49 @@
         <v>0</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
-        <v>-100</v>
-      </c>
       <c r="X89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Y89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AF89" s="3">
         <v>400</v>
       </c>
       <c r="AG89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-300</v>
       </c>
-      <c r="AH89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7974,23 +8195,23 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>8</v>
@@ -8004,8 +8225,8 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8017,13 +8238,16 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8244,17 +8474,17 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>100</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
+        <v>100</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
@@ -8262,11 +8492,11 @@
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
@@ -8274,24 +8504,24 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="X94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -8311,13 +8541,16 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>700</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8780,23 +9026,23 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8813,22 +9059,22 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>4400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -8837,13 +9083,16 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-700</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,16 +9189,19 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -8967,10 +9219,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -8979,11 +9231,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
@@ -9000,25 +9252,25 @@
         <v>0</v>
       </c>
       <c r="V102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
       <c r="Y102" s="3">
         <v>100</v>
       </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -9027,15 +9279,18 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -865,16 +869,16 @@
         <v>0</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
-        <v>100</v>
-      </c>
       <c r="AA8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="3">
         <v>200</v>
@@ -889,42 +893,45 @@
         <v>200</v>
       </c>
       <c r="AF8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG8" s="3">
         <v>400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>8</v>
@@ -953,17 +960,17 @@
       <c r="S9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="3">
-        <v>200</v>
+      <c r="T9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U9" s="3">
         <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>200</v>
@@ -972,16 +979,16 @@
         <v>200</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>200</v>
       </c>
       <c r="AC9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD9" s="3">
         <v>300</v>
@@ -990,42 +997,45 @@
         <v>300</v>
       </c>
       <c r="AF9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG9" s="3">
         <v>500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>8</v>
@@ -1054,23 +1064,23 @@
       <c r="S10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="3">
-        <v>-200</v>
+      <c r="T10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U10" s="3">
         <v>-200</v>
       </c>
       <c r="V10" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="W10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X10" s="3">
         <v>-200</v>
       </c>
-      <c r="X10" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z10" s="3">
         <v>0</v>
@@ -1082,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="AC10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
         <v>-100</v>
@@ -1097,13 +1107,16 @@
         <v>-100</v>
       </c>
       <c r="AH10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI10" s="3">
         <v>-400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1382,8 +1402,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1400,23 +1420,23 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1424,26 +1444,29 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2600</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-900</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,8 +1603,9 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1643,48 +1670,51 @@
         <v>100</v>
       </c>
       <c r="X17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y17" s="3">
         <v>300</v>
       </c>
       <c r="Z17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA17" s="3">
         <v>200</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>300</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
         <v>-100</v>
@@ -1708,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
@@ -1744,11 +1774,11 @@
         <v>-100</v>
       </c>
       <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>-100</v>
-      </c>
       <c r="Z18" s="3">
         <v>-100</v>
       </c>
@@ -1759,28 +1789,31 @@
         <v>-100</v>
       </c>
       <c r="AC18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,41 +1849,42 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
@@ -1858,20 +1892,20 @@
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
-        <v>100</v>
-      </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
@@ -1882,16 +1916,16 @@
         <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1900,45 +1934,48 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-100</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1947,34 +1984,34 @@
         <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
         <v>100</v>
       </c>
       <c r="R21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V21" s="3">
         <v>0</v>
@@ -1983,43 +2020,46 @@
         <v>0</v>
       </c>
       <c r="X21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>200</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
       <c r="AB21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="3">
         <v>-100</v>
       </c>
       <c r="AD21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
       <c r="AF21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3">
         <v>700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2041,8 +2081,8 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,8 +2159,11 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2149,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23" s="3">
         <v>0</v>
@@ -2164,19 +2207,19 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V23" s="3">
         <v>0</v>
@@ -2185,66 +2228,69 @@
         <v>0</v>
       </c>
       <c r="X23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
         <v>100</v>
       </c>
       <c r="Z23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
         <v>-100</v>
       </c>
       <c r="AB23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,8 +2471,11 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2452,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26" s="3">
         <v>0</v>
@@ -2467,19 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V26" s="3">
         <v>0</v>
@@ -2488,43 +2540,46 @@
         <v>0</v>
       </c>
       <c r="X26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
         <v>100</v>
       </c>
       <c r="Z26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
         <v>-100</v>
       </c>
       <c r="AB26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2553,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
@@ -2568,19 +2623,19 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
@@ -2589,43 +2644,46 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>100</v>
       </c>
       <c r="Z27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-200</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2754,14 +2815,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2776,28 +2837,28 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>2100</v>
       </c>
-      <c r="T29" s="3">
-        <v>-100</v>
-      </c>
       <c r="U29" s="3">
         <v>-100</v>
       </c>
       <c r="V29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-2300</v>
       </c>
-      <c r="X29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,41 +3095,44 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
@@ -3070,20 +3140,20 @@
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
-        <v>-100</v>
-      </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
@@ -3094,16 +3164,16 @@
         <v>-100</v>
       </c>
       <c r="X32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -3112,25 +3182,28 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3159,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" s="3">
         <v>0</v>
@@ -3174,64 +3247,67 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
-        <v>-100</v>
-      </c>
       <c r="U33" s="3">
         <v>-100</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA33" s="3">
         <v>-100</v>
       </c>
       <c r="AB33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-200</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,8 +3407,11 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3361,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" s="3">
         <v>0</v>
@@ -3376,170 +3455,176 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
-        <v>-100</v>
-      </c>
       <c r="U35" s="3">
         <v>-100</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA35" s="3">
         <v>-100</v>
       </c>
       <c r="AB35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-200</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3698,9 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3627,10 +3714,10 @@
         <v>400</v>
       </c>
       <c r="G41" s="3">
+        <v>400</v>
+      </c>
+      <c r="H41" s="3">
         <v>500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>400</v>
       </c>
       <c r="I41" s="3">
         <v>400</v>
@@ -3645,20 +3732,20 @@
         <v>400</v>
       </c>
       <c r="M41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N41" s="3">
         <v>300</v>
       </c>
       <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
@@ -3678,22 +3765,22 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>400</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>300</v>
       </c>
       <c r="AB41" s="3">
         <v>300</v>
       </c>
       <c r="AC41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD41" s="3">
         <v>400</v>
@@ -3705,16 +3792,19 @@
         <v>400</v>
       </c>
       <c r="AG41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
-        <v>100</v>
-      </c>
       <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3831,8 +3924,8 @@
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="3">
-        <v>3500</v>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I43" s="3">
         <v>3500</v>
@@ -3847,7 +3940,7 @@
         <v>3500</v>
       </c>
       <c r="M43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="N43" s="3">
         <v>3600</v>
@@ -3856,46 +3949,46 @@
         <v>3600</v>
       </c>
       <c r="P43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q43" s="3">
         <v>3700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4200</v>
       </c>
-      <c r="Z43" s="3">
-        <v>100</v>
-      </c>
       <c r="AA43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
       <c r="AC43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="3">
         <v>100</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>100</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,8 +4112,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4025,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -4037,10 +4136,10 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4061,16 +4160,16 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -4088,13 +4187,13 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>4100</v>
       </c>
-      <c r="AA45" s="3">
-        <v>100</v>
-      </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -4103,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="AE45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="3">
         <v>100</v>
@@ -4112,13 +4211,16 @@
         <v>100</v>
       </c>
       <c r="AH45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI45" s="3">
         <v>200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4135,7 +4237,7 @@
         <v>500</v>
       </c>
       <c r="H46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="I46" s="3">
         <v>4000</v>
@@ -4150,22 +4252,22 @@
         <v>4000</v>
       </c>
       <c r="M46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N46" s="3">
         <v>3900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3900</v>
-      </c>
-      <c r="R46" s="3">
-        <v>3800</v>
       </c>
       <c r="S46" s="3">
         <v>3800</v>
@@ -4174,66 +4276,69 @@
         <v>3800</v>
       </c>
       <c r="U46" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="V46" s="3">
         <v>4100</v>
       </c>
       <c r="W46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X46" s="3">
         <v>4300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4500</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>400</v>
       </c>
       <c r="AB46" s="3">
         <v>400</v>
       </c>
       <c r="AC46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD46" s="3">
         <v>500</v>
       </c>
       <c r="AE46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF46" s="3">
         <v>600</v>
-      </c>
-      <c r="AF46" s="3">
-        <v>700</v>
       </c>
       <c r="AG46" s="3">
         <v>700</v>
       </c>
       <c r="AH46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI46" s="3">
         <v>400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3500</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4253,8 +4358,8 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4361,7 +4469,7 @@
         <v>600</v>
       </c>
       <c r="P48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q48" s="3">
         <v>700</v>
@@ -4373,7 +4481,7 @@
         <v>700</v>
       </c>
       <c r="T48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="U48" s="3">
         <v>1400</v>
@@ -4382,46 +4490,49 @@
         <v>1400</v>
       </c>
       <c r="W48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X48" s="3">
         <v>1500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>3100</v>
       </c>
       <c r="Z48" s="3">
         <v>3100</v>
       </c>
       <c r="AA48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3300</v>
       </c>
       <c r="AC48" s="3">
         <v>3300</v>
       </c>
       <c r="AD48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6200</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>6300</v>
       </c>
       <c r="AH48" s="3">
         <v>6300</v>
       </c>
       <c r="AI48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4840,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>3500</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4765,13 +4885,13 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -4783,10 +4903,10 @@
         <v>200</v>
       </c>
       <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>1100</v>
-      </c>
-      <c r="W52" s="3">
-        <v>200</v>
       </c>
       <c r="X52" s="3">
         <v>200</v>
@@ -4795,7 +4915,7 @@
         <v>200</v>
       </c>
       <c r="Z52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA52" s="3">
         <v>300</v>
@@ -4819,13 +4939,16 @@
         <v>300</v>
       </c>
       <c r="AH52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI52" s="3">
         <v>400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,8 +5048,11 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4940,16 +5066,16 @@
         <v>4600</v>
       </c>
       <c r="G54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H54" s="3">
         <v>4700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4700</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4600</v>
       </c>
       <c r="K54" s="3">
         <v>4600</v>
@@ -4958,7 +5084,7 @@
         <v>4600</v>
       </c>
       <c r="M54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="N54" s="3">
         <v>4500</v>
@@ -4967,67 +5093,70 @@
         <v>4500</v>
       </c>
       <c r="P54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q54" s="3">
         <v>4800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4700</v>
-      </c>
-      <c r="R54" s="3">
-        <v>4600</v>
       </c>
       <c r="S54" s="3">
         <v>4600</v>
       </c>
       <c r="T54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="U54" s="3">
         <v>5400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,8 +5230,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5121,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5133,10 +5264,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -5154,20 +5285,20 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
-        <v>100</v>
-      </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
@@ -5175,34 +5306,37 @@
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5243,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
@@ -5252,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5264,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
@@ -5300,33 +5434,36 @@
         <v>100</v>
       </c>
       <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5341,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
@@ -5356,13 +5493,13 @@
         <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -5383,19 +5520,19 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
@@ -5403,8 +5540,11 @@
       <c r="AI59" s="3">
         <v>100</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5445,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="P60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
@@ -5454,43 +5594,43 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T60" s="3">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
-        <v>100</v>
-      </c>
       <c r="Y60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>200</v>
       </c>
       <c r="AA60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AB60" s="3">
         <v>400</v>
       </c>
       <c r="AC60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AD60" s="3">
         <v>600</v>
       </c>
       <c r="AE60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AF60" s="3">
         <v>700</v>
@@ -5499,13 +5639,16 @@
         <v>700</v>
       </c>
       <c r="AH60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI60" s="3">
         <v>400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5546,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -5555,7 +5698,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>200</v>
@@ -5591,7 +5734,7 @@
         <v>200</v>
       </c>
       <c r="AE61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF61" s="3">
         <v>300</v>
@@ -5603,33 +5746,36 @@
         <v>300</v>
       </c>
       <c r="AI61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5659,16 +5805,16 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2900</v>
-      </c>
-      <c r="W62" s="3">
-        <v>2800</v>
       </c>
       <c r="X62" s="3">
         <v>2800</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>2800</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,8 +6164,11 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6051,7 +6209,7 @@
         <v>100</v>
       </c>
       <c r="P66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q66" s="3">
         <v>300</v>
@@ -6060,43 +6218,43 @@
         <v>300</v>
       </c>
       <c r="S66" s="3">
+        <v>300</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3200</v>
-      </c>
-      <c r="U66" s="3">
-        <v>3400</v>
       </c>
       <c r="V66" s="3">
         <v>3400</v>
       </c>
       <c r="W66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X66" s="3">
         <v>3600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3100</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>3400</v>
       </c>
       <c r="AB66" s="3">
         <v>3400</v>
       </c>
       <c r="AC66" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="AD66" s="3">
         <v>3600</v>
       </c>
       <c r="AE66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AF66" s="3">
         <v>3700</v>
@@ -6105,13 +6263,16 @@
         <v>3700</v>
       </c>
       <c r="AH66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AI66" s="3">
         <v>3500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,8 +6722,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6566,7 +6740,7 @@
         <v>-59100</v>
       </c>
       <c r="G72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="H72" s="3">
         <v>-59000</v>
@@ -6575,7 +6749,7 @@
         <v>-59000</v>
       </c>
       <c r="J72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="K72" s="3">
         <v>-59100</v>
@@ -6584,7 +6758,7 @@
         <v>-59100</v>
       </c>
       <c r="M72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="N72" s="3">
         <v>-59200</v>
@@ -6599,61 +6773,64 @@
         <v>-59200</v>
       </c>
       <c r="R72" s="3">
-        <v>-59300</v>
+        <v>-59200</v>
       </c>
       <c r="S72" s="3">
         <v>-59300</v>
       </c>
       <c r="T72" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="U72" s="3">
         <v>-61500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-61300</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-61200</v>
       </c>
       <c r="W72" s="3">
         <v>-61200</v>
       </c>
       <c r="X72" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-58900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-58700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,8 +7138,11 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6985,10 +7171,10 @@
         <v>4600</v>
       </c>
       <c r="L76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M76" s="3">
         <v>4500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>4400</v>
       </c>
       <c r="N76" s="3">
         <v>4400</v>
@@ -6997,67 +7183,70 @@
         <v>4400</v>
       </c>
       <c r="P76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q76" s="3">
         <v>4500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2300</v>
-      </c>
-      <c r="V76" s="3">
-        <v>2400</v>
       </c>
       <c r="W76" s="3">
         <v>2400</v>
       </c>
       <c r="X76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y76" s="3">
         <v>4700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>400</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>500</v>
       </c>
       <c r="AC76" s="3">
         <v>500</v>
       </c>
       <c r="AD76" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE76" s="3">
         <v>600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,114 +7346,120 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7293,10 +7488,10 @@
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N81" s="3">
         <v>0</v>
@@ -7308,64 +7503,67 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
-        <v>-100</v>
-      </c>
       <c r="U81" s="3">
         <v>-100</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AA81" s="3">
         <v>-100</v>
       </c>
       <c r="AB81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-200</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7452,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7473,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -7491,19 +7690,22 @@
         <v>100</v>
       </c>
       <c r="AF83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3">
-        <v>100</v>
-      </c>
       <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8221,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8016,10 +8233,10 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G89" s="3">
         <v>0</v>
@@ -8037,32 +8254,32 @@
         <v>0</v>
       </c>
       <c r="L89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
@@ -8070,46 +8287,49 @@
         <v>0</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>500</v>
       </c>
-      <c r="X89" s="3">
-        <v>-100</v>
-      </c>
       <c r="Y89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Z89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
       <c r="AF89" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AG89" s="3">
         <v>400</v>
       </c>
       <c r="AH89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8198,23 +8419,23 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
@@ -8228,8 +8449,8 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8241,13 +8462,16 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,19 +8675,22 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -8468,26 +8698,26 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
-        <v>100</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
+        <v>100</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
@@ -8495,11 +8725,11 @@
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
@@ -8507,24 +8737,24 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Y94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -8544,13 +8774,16 @@
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9233,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9029,23 +9275,23 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -9062,22 +9308,22 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>4400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -9086,36 +9332,39 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,8 +9441,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9201,10 +9453,10 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
@@ -9222,10 +9474,10 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -9234,11 +9486,11 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
@@ -9255,25 +9507,25 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
         <v>100</v>
       </c>
       <c r="AA102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
@@ -9282,15 +9534,18 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -830,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -872,16 +875,16 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>100</v>
-      </c>
       <c r="AB8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC8" s="3">
         <v>200</v>
@@ -896,19 +899,22 @@
         <v>200</v>
       </c>
       <c r="AG8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH8" s="3">
         <v>400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,8 +939,8 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>8</v>
@@ -963,17 +969,17 @@
       <c r="T9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="3">
-        <v>200</v>
+      <c r="U9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V9" s="3">
         <v>200</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>200</v>
@@ -982,16 +988,16 @@
         <v>200</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="3">
         <v>200</v>
       </c>
       <c r="AD9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE9" s="3">
         <v>300</v>
@@ -1000,19 +1006,22 @@
         <v>300</v>
       </c>
       <c r="AG9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH9" s="3">
         <v>500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,8 +1046,8 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>8</v>
@@ -1067,23 +1076,23 @@
       <c r="T10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="3">
-        <v>-200</v>
+      <c r="U10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V10" s="3">
         <v>-200</v>
       </c>
       <c r="W10" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-200</v>
       </c>
-      <c r="Y10" s="3">
-        <v>-100</v>
-      </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1095,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3">
         <v>-100</v>
@@ -1110,13 +1119,16 @@
         <v>-100</v>
       </c>
       <c r="AI10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1405,8 +1424,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1423,23 +1442,23 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1447,26 +1466,29 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>2600</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1673,43 +1699,46 @@
         <v>100</v>
       </c>
       <c r="Y17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z17" s="3">
         <v>300</v>
       </c>
       <c r="AA17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB17" s="3">
         <v>200</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>300</v>
       </c>
       <c r="AC17" s="3">
         <v>300</v>
       </c>
       <c r="AD17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1732,7 +1761,7 @@
         <v>-100</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1741,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
@@ -1777,11 +1806,11 @@
         <v>-100</v>
       </c>
       <c r="Y18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
-      <c r="Z18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA18" s="3">
         <v>-100</v>
       </c>
@@ -1792,28 +1821,31 @@
         <v>-100</v>
       </c>
       <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,13 +1882,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1876,18 +1909,18 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
@@ -1895,20 +1928,20 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
-        <v>100</v>
-      </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
@@ -1919,16 +1952,16 @@
         <v>100</v>
       </c>
       <c r="Y20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
@@ -1937,25 +1970,28 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
       <c r="AI20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1963,22 +1999,22 @@
         <v>-100</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
         <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1987,34 +2023,34 @@
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
         <v>100</v>
       </c>
       <c r="S21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
@@ -2023,43 +2059,46 @@
         <v>0</v>
       </c>
       <c r="Y21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>200</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
       <c r="AB21" s="3">
         <v>0</v>
       </c>
       <c r="AC21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="3">
         <v>-100</v>
       </c>
       <c r="AE21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
       <c r="AG21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,8 +2201,11 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2195,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
@@ -2210,19 +2252,19 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
@@ -2231,43 +2273,46 @@
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3">
         <v>100</v>
       </c>
       <c r="AA23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB23" s="3">
         <v>-100</v>
       </c>
       <c r="AC23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,8 +2337,8 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2507,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
@@ -2522,19 +2573,19 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2543,43 +2594,46 @@
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3">
         <v>100</v>
       </c>
       <c r="AA26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB26" s="3">
         <v>-100</v>
       </c>
       <c r="AC26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
-      <c r="AI26" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2611,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27" s="3">
         <v>0</v>
@@ -2626,19 +2680,19 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2647,43 +2701,46 @@
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3">
         <v>100</v>
       </c>
       <c r="AA27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB27" s="3">
         <v>-100</v>
       </c>
       <c r="AC27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
-      <c r="AI27" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2818,14 +2878,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2840,28 +2900,28 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>2100</v>
       </c>
-      <c r="U29" s="3">
-        <v>-100</v>
-      </c>
       <c r="V29" s="3">
         <v>-100</v>
       </c>
       <c r="W29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,13 +3164,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3124,18 +3193,18 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
@@ -3143,20 +3212,20 @@
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
-        <v>-100</v>
-      </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
@@ -3167,16 +3236,16 @@
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
@@ -3185,25 +3254,28 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
       <c r="AI32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3235,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
@@ -3250,64 +3322,67 @@
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
-        <v>-100</v>
-      </c>
       <c r="V33" s="3">
         <v>-100</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>-100</v>
       </c>
       <c r="AC33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3443,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
@@ -3458,173 +3536,179 @@
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
-        <v>-100</v>
-      </c>
       <c r="V35" s="3">
         <v>-100</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>-100</v>
       </c>
       <c r="AC35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,8 +3784,9 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3717,10 +3803,10 @@
         <v>400</v>
       </c>
       <c r="H41" s="3">
+        <v>400</v>
+      </c>
+      <c r="I41" s="3">
         <v>500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>400</v>
       </c>
       <c r="J41" s="3">
         <v>400</v>
@@ -3735,20 +3821,20 @@
         <v>400</v>
       </c>
       <c r="N41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
       </c>
       <c r="P41" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
@@ -3768,22 +3854,22 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>400</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>300</v>
       </c>
       <c r="AC41" s="3">
         <v>300</v>
       </c>
       <c r="AD41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE41" s="3">
         <v>400</v>
@@ -3795,16 +3881,19 @@
         <v>400</v>
       </c>
       <c r="AH41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
-      <c r="AI41" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK41" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,8 +3996,11 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3927,8 +4019,8 @@
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
-        <v>3500</v>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3">
         <v>3500</v>
@@ -3943,7 +4035,7 @@
         <v>3500</v>
       </c>
       <c r="N43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="O43" s="3">
         <v>3600</v>
@@ -3952,46 +4044,46 @@
         <v>3600</v>
       </c>
       <c r="Q43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R43" s="3">
         <v>3700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4200</v>
       </c>
-      <c r="AA43" s="3">
-        <v>100</v>
-      </c>
       <c r="AB43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>100</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>100</v>
       </c>
+      <c r="AK43" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4127,10 +4225,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -4139,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4163,16 +4261,16 @@
         <v>0</v>
       </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>100</v>
-      </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -4190,13 +4288,13 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>4100</v>
       </c>
-      <c r="AB45" s="3">
-        <v>100</v>
-      </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -4205,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="AF45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG45" s="3">
         <v>100</v>
@@ -4214,18 +4312,21 @@
         <v>100</v>
       </c>
       <c r="AI45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E46" s="3">
         <v>500</v>
@@ -4240,7 +4341,7 @@
         <v>500</v>
       </c>
       <c r="I46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="J46" s="3">
         <v>4000</v>
@@ -4255,22 +4356,22 @@
         <v>4000</v>
       </c>
       <c r="N46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O46" s="3">
         <v>3900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3900</v>
-      </c>
-      <c r="S46" s="3">
-        <v>3800</v>
       </c>
       <c r="T46" s="3">
         <v>3800</v>
@@ -4279,52 +4380,55 @@
         <v>3800</v>
       </c>
       <c r="V46" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="W46" s="3">
         <v>4100</v>
       </c>
       <c r="X46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>4300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4500</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>400</v>
       </c>
       <c r="AC46" s="3">
         <v>400</v>
       </c>
       <c r="AD46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE46" s="3">
         <v>500</v>
       </c>
       <c r="AF46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG46" s="3">
         <v>600</v>
-      </c>
-      <c r="AG46" s="3">
-        <v>700</v>
       </c>
       <c r="AH46" s="3">
         <v>700</v>
       </c>
       <c r="AI46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4361,8 +4465,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4427,8 +4531,11 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4472,7 +4579,7 @@
         <v>600</v>
       </c>
       <c r="Q48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R48" s="3">
         <v>700</v>
@@ -4484,7 +4591,7 @@
         <v>700</v>
       </c>
       <c r="U48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="V48" s="3">
         <v>1400</v>
@@ -4493,46 +4600,49 @@
         <v>1400</v>
       </c>
       <c r="X48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3200</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>3100</v>
       </c>
       <c r="AA48" s="3">
         <v>3100</v>
       </c>
       <c r="AB48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>3300</v>
       </c>
       <c r="AD48" s="3">
         <v>3300</v>
       </c>
       <c r="AE48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AF48" s="3">
         <v>3400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6200</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>6300</v>
       </c>
       <c r="AI48" s="3">
         <v>6300</v>
       </c>
       <c r="AJ48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AK48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,13 +4959,16 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="E52" s="3">
         <v>3500</v>
@@ -4863,14 +4982,14 @@
       <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>3500</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4888,13 +5007,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
       </c>
       <c r="S52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
@@ -4906,10 +5025,10 @@
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>1100</v>
-      </c>
-      <c r="X52" s="3">
-        <v>200</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
@@ -4918,7 +5037,7 @@
         <v>200</v>
       </c>
       <c r="AA52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>300</v>
@@ -4942,13 +5061,16 @@
         <v>300</v>
       </c>
       <c r="AI52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,8 +5173,11 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5069,16 +5194,16 @@
         <v>4600</v>
       </c>
       <c r="H54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I54" s="3">
         <v>4700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>4600</v>
       </c>
       <c r="L54" s="3">
         <v>4600</v>
@@ -5087,7 +5212,7 @@
         <v>4600</v>
       </c>
       <c r="N54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="O54" s="3">
         <v>4500</v>
@@ -5096,67 +5221,70 @@
         <v>4500</v>
       </c>
       <c r="Q54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="R54" s="3">
         <v>4800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4700</v>
-      </c>
-      <c r="S54" s="3">
-        <v>4600</v>
       </c>
       <c r="T54" s="3">
         <v>4600</v>
       </c>
       <c r="U54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="V54" s="3">
         <v>5400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,8 +5360,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5255,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5267,10 +5397,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -5288,20 +5418,20 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
-        <v>100</v>
-      </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
@@ -5309,34 +5439,37 @@
         <v>100</v>
       </c>
       <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5380,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
@@ -5389,7 +5522,7 @@
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5401,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>100</v>
@@ -5437,10 +5570,13 @@
         <v>100</v>
       </c>
       <c r="AJ58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5465,8 +5601,8 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5481,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
@@ -5496,13 +5632,13 @@
         <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -5523,19 +5659,19 @@
         <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3">
         <v>100</v>
@@ -5543,8 +5679,11 @@
       <c r="AJ59" s="3">
         <v>100</v>
       </c>
+      <c r="AK59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5588,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="Q60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R60" s="3">
         <v>200</v>
@@ -5597,43 +5736,43 @@
         <v>200</v>
       </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U60" s="3">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="Y60" s="3">
-        <v>100</v>
-      </c>
       <c r="Z60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA60" s="3">
         <v>200</v>
       </c>
       <c r="AB60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AC60" s="3">
         <v>400</v>
       </c>
       <c r="AD60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AE60" s="3">
         <v>600</v>
       </c>
       <c r="AF60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AG60" s="3">
         <v>700</v>
@@ -5642,13 +5781,16 @@
         <v>700</v>
       </c>
       <c r="AI60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5692,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -5701,7 +5843,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>200</v>
@@ -5737,7 +5879,7 @@
         <v>200</v>
       </c>
       <c r="AF61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG61" s="3">
         <v>300</v>
@@ -5749,10 +5891,13 @@
         <v>300</v>
       </c>
       <c r="AJ61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,8 +5922,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5808,16 +5953,16 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>2800</v>
       </c>
       <c r="Y62" s="3">
         <v>2800</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>2800</v>
       </c>
+      <c r="AK62" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,8 +6321,11 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6212,7 +6369,7 @@
         <v>100</v>
       </c>
       <c r="Q66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R66" s="3">
         <v>300</v>
@@ -6221,43 +6378,43 @@
         <v>300</v>
       </c>
       <c r="T66" s="3">
+        <v>300</v>
+      </c>
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>3400</v>
       </c>
       <c r="W66" s="3">
         <v>3400</v>
       </c>
       <c r="X66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Y66" s="3">
         <v>3600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>3400</v>
       </c>
       <c r="AC66" s="3">
         <v>3400</v>
       </c>
       <c r="AD66" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="AE66" s="3">
         <v>3600</v>
       </c>
       <c r="AF66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AG66" s="3">
         <v>3700</v>
@@ -6266,13 +6423,16 @@
         <v>3700</v>
       </c>
       <c r="AI66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6743,7 +6916,7 @@
         <v>-59100</v>
       </c>
       <c r="H72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="I72" s="3">
         <v>-59000</v>
@@ -6752,7 +6925,7 @@
         <v>-59000</v>
       </c>
       <c r="K72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="L72" s="3">
         <v>-59100</v>
@@ -6761,7 +6934,7 @@
         <v>-59100</v>
       </c>
       <c r="N72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="O72" s="3">
         <v>-59200</v>
@@ -6776,61 +6949,64 @@
         <v>-59200</v>
       </c>
       <c r="S72" s="3">
-        <v>-59300</v>
+        <v>-59200</v>
       </c>
       <c r="T72" s="3">
         <v>-59300</v>
       </c>
       <c r="U72" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="V72" s="3">
         <v>-61500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-61300</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-61200</v>
       </c>
       <c r="X72" s="3">
         <v>-61200</v>
       </c>
       <c r="Y72" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-58900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,13 +7323,16 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E76" s="3">
         <v>4600</v>
@@ -7174,10 +7359,10 @@
         <v>4600</v>
       </c>
       <c r="M76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N76" s="3">
         <v>4500</v>
-      </c>
-      <c r="N76" s="3">
-        <v>4400</v>
       </c>
       <c r="O76" s="3">
         <v>4400</v>
@@ -7186,67 +7371,70 @@
         <v>4400</v>
       </c>
       <c r="Q76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R76" s="3">
         <v>4500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2300</v>
-      </c>
-      <c r="W76" s="3">
-        <v>2400</v>
       </c>
       <c r="X76" s="3">
         <v>2400</v>
       </c>
       <c r="Y76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z76" s="3">
         <v>4700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>400</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>500</v>
       </c>
       <c r="AD76" s="3">
         <v>500</v>
       </c>
       <c r="AE76" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF76" s="3">
         <v>600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7491,10 +7685,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O81" s="3">
         <v>0</v>
@@ -7506,64 +7700,67 @@
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
-        <v>-100</v>
-      </c>
       <c r="V81" s="3">
         <v>-100</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>-100</v>
       </c>
       <c r="AC81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AE81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
-      <c r="AI81" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7654,10 +7852,10 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7675,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
@@ -7693,19 +7891,22 @@
         <v>100</v>
       </c>
       <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3">
-        <v>100</v>
-      </c>
       <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,22 +8437,25 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>0</v>
@@ -8257,32 +8473,32 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
@@ -8290,46 +8506,49 @@
         <v>0</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>500</v>
       </c>
-      <c r="Y89" s="3">
-        <v>-100</v>
-      </c>
       <c r="Z89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AA89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
       <c r="AG89" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AH89" s="3">
         <v>400</v>
       </c>
       <c r="AI89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8380,11 +8600,11 @@
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8422,23 +8642,23 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -8452,8 +8672,8 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -8465,13 +8685,16 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8692,35 +8921,35 @@
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>100</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
+        <v>100</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
@@ -8728,11 +8957,11 @@
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
@@ -8740,24 +8969,24 @@
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -8777,13 +9006,16 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9262,8 +9507,8 @@
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9278,23 +9523,23 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -9311,22 +9556,22 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>4400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
@@ -9335,13 +9580,16 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9456,10 +9707,10 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>0</v>
@@ -9477,10 +9728,10 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -9489,11 +9740,11 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -9510,25 +9761,25 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
-        <v>100</v>
-      </c>
       <c r="AA102" s="3">
         <v>100</v>
       </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -9537,15 +9788,18 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -836,13 +840,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -878,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>100</v>
-      </c>
       <c r="AC8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD8" s="3">
         <v>200</v>
@@ -902,19 +906,22 @@
         <v>200</v>
       </c>
       <c r="AH8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI8" s="3">
         <v>400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,8 +949,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>8</v>
@@ -972,17 +979,17 @@
       <c r="U9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V9" s="3">
-        <v>200</v>
+      <c r="V9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W9" s="3">
         <v>200</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
         <v>200</v>
@@ -991,16 +998,16 @@
         <v>200</v>
       </c>
       <c r="AB9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
         <v>200</v>
       </c>
       <c r="AE9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF9" s="3">
         <v>300</v>
@@ -1009,19 +1016,22 @@
         <v>300</v>
       </c>
       <c r="AH9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI9" s="3">
         <v>500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,8 +1059,8 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>8</v>
@@ -1079,23 +1089,23 @@
       <c r="U10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V10" s="3">
-        <v>-200</v>
+      <c r="V10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W10" s="3">
         <v>-200</v>
       </c>
       <c r="X10" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>-200</v>
       </c>
-      <c r="Z10" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB10" s="3">
         <v>0</v>
@@ -1107,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="3">
         <v>-100</v>
@@ -1122,13 +1132,16 @@
         <v>-100</v>
       </c>
       <c r="AJ10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK10" s="3">
         <v>-400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1427,8 +1447,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1445,23 +1465,23 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1469,26 +1489,29 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>2600</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-900</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1702,43 +1729,46 @@
         <v>100</v>
       </c>
       <c r="Z17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="3">
         <v>300</v>
       </c>
       <c r="AB17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC17" s="3">
         <v>200</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>300</v>
       </c>
       <c r="AD17" s="3">
         <v>300</v>
       </c>
       <c r="AE17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1764,7 +1794,7 @@
         <v>-100</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
@@ -1773,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
         <v>-100</v>
@@ -1809,11 +1839,11 @@
         <v>-100</v>
       </c>
       <c r="Z18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AB18" s="3">
         <v>-100</v>
       </c>
@@ -1824,28 +1854,31 @@
         <v>-100</v>
       </c>
       <c r="AE18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,16 +1916,17 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -1912,18 +1946,18 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
@@ -1931,20 +1965,20 @@
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>100</v>
-      </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
@@ -1955,16 +1989,16 @@
         <v>100</v>
       </c>
       <c r="Z20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1973,25 +2007,28 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2002,22 +2039,22 @@
         <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
@@ -2026,34 +2063,34 @@
         <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <v>100</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X21" s="3">
         <v>0</v>
@@ -2062,43 +2099,46 @@
         <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB21" s="3">
         <v>200</v>
       </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
       <c r="AC21" s="3">
         <v>0</v>
       </c>
       <c r="AD21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="3">
         <v>-100</v>
       </c>
       <c r="AF21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG21" s="3">
-        <v>0</v>
-      </c>
       <c r="AH21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3">
         <v>700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,8 +2244,11 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2240,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23" s="3">
         <v>0</v>
@@ -2255,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
@@ -2276,43 +2319,46 @@
         <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3">
         <v>100</v>
       </c>
       <c r="AB23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC23" s="3">
         <v>-100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,8 +2386,8 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2561,10 +2613,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3">
         <v>0</v>
@@ -2576,19 +2628,19 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
@@ -2597,43 +2649,46 @@
         <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3">
         <v>100</v>
       </c>
       <c r="AB26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC26" s="3">
         <v>-100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
       <c r="AK26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2668,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" s="3">
         <v>0</v>
@@ -2683,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
@@ -2704,43 +2759,46 @@
         <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3">
         <v>100</v>
       </c>
       <c r="AB27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC27" s="3">
         <v>-100</v>
       </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
       <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2881,14 +2942,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2903,28 +2964,28 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>2100</v>
       </c>
-      <c r="V29" s="3">
-        <v>-100</v>
-      </c>
       <c r="W29" s="3">
         <v>-100</v>
       </c>
       <c r="X29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,16 +3234,19 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -3196,18 +3266,18 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
@@ -3215,20 +3285,20 @@
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>-100</v>
-      </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
@@ -3239,16 +3309,16 @@
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -3257,25 +3327,28 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
       <c r="AJ32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3310,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
@@ -3325,64 +3398,67 @@
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
-        <v>-100</v>
-      </c>
       <c r="W33" s="3">
         <v>-100</v>
       </c>
       <c r="X33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
       <c r="AA33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC33" s="3">
         <v>-100</v>
       </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3524,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>0</v>
@@ -3539,176 +3618,182 @@
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
-        <v>-100</v>
-      </c>
       <c r="W35" s="3">
         <v>-100</v>
       </c>
       <c r="X35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
       <c r="AA35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC35" s="3">
         <v>-100</v>
       </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,13 +3871,14 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
@@ -3806,10 +3893,10 @@
         <v>400</v>
       </c>
       <c r="I41" s="3">
+        <v>400</v>
+      </c>
+      <c r="J41" s="3">
         <v>500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>400</v>
       </c>
       <c r="K41" s="3">
         <v>400</v>
@@ -3824,20 +3911,20 @@
         <v>400</v>
       </c>
       <c r="O41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P41" s="3">
         <v>300</v>
       </c>
       <c r="Q41" s="3">
+        <v>300</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -3857,22 +3944,22 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>400</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>300</v>
       </c>
       <c r="AD41" s="3">
         <v>300</v>
       </c>
       <c r="AE41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF41" s="3">
         <v>400</v>
@@ -3884,16 +3971,19 @@
         <v>400</v>
       </c>
       <c r="AI41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>500</v>
       </c>
-      <c r="AJ41" s="3">
-        <v>100</v>
-      </c>
       <c r="AK41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL41" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,8 +4089,11 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4022,8 +4115,8 @@
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
-        <v>3500</v>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K43" s="3">
         <v>3500</v>
@@ -4038,7 +4131,7 @@
         <v>3500</v>
       </c>
       <c r="O43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="P43" s="3">
         <v>3600</v>
@@ -4047,46 +4140,46 @@
         <v>3600</v>
       </c>
       <c r="R43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S43" s="3">
         <v>3700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4200</v>
       </c>
-      <c r="AB43" s="3">
-        <v>100</v>
-      </c>
       <c r="AC43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="3">
         <v>100</v>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>100</v>
       </c>
+      <c r="AL43" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,13 +4309,16 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -4228,10 +4327,10 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -4240,10 +4339,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4264,16 +4363,16 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
-        <v>100</v>
-      </c>
       <c r="U45" s="3">
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -4291,13 +4390,13 @@
         <v>0</v>
       </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>4100</v>
       </c>
-      <c r="AC45" s="3">
-        <v>100</v>
-      </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -4306,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="3">
         <v>100</v>
@@ -4315,13 +4414,16 @@
         <v>100</v>
       </c>
       <c r="AJ45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK45" s="3">
         <v>200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4329,7 +4431,7 @@
         <v>400</v>
       </c>
       <c r="E46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F46" s="3">
         <v>500</v>
@@ -4344,7 +4446,7 @@
         <v>500</v>
       </c>
       <c r="J46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="K46" s="3">
         <v>4000</v>
@@ -4359,22 +4461,22 @@
         <v>4000</v>
       </c>
       <c r="O46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P46" s="3">
         <v>3900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3900</v>
-      </c>
-      <c r="T46" s="3">
-        <v>3800</v>
       </c>
       <c r="U46" s="3">
         <v>3800</v>
@@ -4383,52 +4485,55 @@
         <v>3800</v>
       </c>
       <c r="W46" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="X46" s="3">
         <v>4100</v>
       </c>
       <c r="Y46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>4300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4500</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>400</v>
       </c>
       <c r="AD46" s="3">
         <v>400</v>
       </c>
       <c r="AE46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AF46" s="3">
         <v>500</v>
       </c>
       <c r="AG46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH46" s="3">
         <v>600</v>
-      </c>
-      <c r="AH46" s="3">
-        <v>700</v>
       </c>
       <c r="AI46" s="3">
         <v>700</v>
       </c>
       <c r="AJ46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK46" s="3">
         <v>400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4468,8 +4573,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4534,8 +4639,11 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4582,7 +4690,7 @@
         <v>600</v>
       </c>
       <c r="R48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S48" s="3">
         <v>700</v>
@@ -4594,7 +4702,7 @@
         <v>700</v>
       </c>
       <c r="V48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="W48" s="3">
         <v>1400</v>
@@ -4603,46 +4711,49 @@
         <v>1400</v>
       </c>
       <c r="Y48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>3100</v>
       </c>
       <c r="AB48" s="3">
         <v>3100</v>
       </c>
       <c r="AC48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>3300</v>
       </c>
       <c r="AE48" s="3">
         <v>3300</v>
       </c>
       <c r="AF48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AG48" s="3">
         <v>3400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6200</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>6300</v>
       </c>
       <c r="AJ48" s="3">
         <v>6300</v>
       </c>
       <c r="AK48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AL48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,16 +5079,19 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E52" s="3">
         <v>3600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3500</v>
       </c>
       <c r="F52" s="3">
         <v>3500</v>
@@ -4985,14 +5105,14 @@
       <c r="I52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="J52" s="3">
+        <v>3500</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5010,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
@@ -5028,10 +5148,10 @@
         <v>200</v>
       </c>
       <c r="X52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>200</v>
       </c>
       <c r="Z52" s="3">
         <v>200</v>
@@ -5040,7 +5160,7 @@
         <v>200</v>
       </c>
       <c r="AB52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC52" s="3">
         <v>300</v>
@@ -5064,13 +5184,16 @@
         <v>300</v>
       </c>
       <c r="AJ52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK52" s="3">
         <v>400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,8 +5299,11 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5197,16 +5323,16 @@
         <v>4600</v>
       </c>
       <c r="I54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J54" s="3">
         <v>4700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>4600</v>
       </c>
       <c r="M54" s="3">
         <v>4600</v>
@@ -5215,7 +5341,7 @@
         <v>4600</v>
       </c>
       <c r="O54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="P54" s="3">
         <v>4500</v>
@@ -5224,67 +5350,70 @@
         <v>4500</v>
       </c>
       <c r="R54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="S54" s="3">
         <v>4800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4700</v>
-      </c>
-      <c r="T54" s="3">
-        <v>4600</v>
       </c>
       <c r="U54" s="3">
         <v>4600</v>
       </c>
       <c r="V54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="W54" s="3">
         <v>5400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,8 +5491,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5388,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5400,10 +5531,10 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -5421,20 +5552,20 @@
         <v>0</v>
       </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
-        <v>100</v>
-      </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
@@ -5442,34 +5573,37 @@
         <v>100</v>
       </c>
       <c r="AC57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5516,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
@@ -5525,7 +5659,7 @@
         <v>100</v>
       </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5537,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>100</v>
@@ -5573,10 +5707,13 @@
         <v>100</v>
       </c>
       <c r="AK58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5604,8 +5741,8 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5620,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
@@ -5635,13 +5772,13 @@
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -5662,19 +5799,19 @@
         <v>0</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ59" s="3">
         <v>100</v>
@@ -5682,13 +5819,16 @@
       <c r="AK59" s="3">
         <v>100</v>
       </c>
+      <c r="AL59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -5730,7 +5870,7 @@
         <v>100</v>
       </c>
       <c r="R60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>200</v>
@@ -5739,43 +5879,43 @@
         <v>200</v>
       </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V60" s="3">
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3">
-        <v>100</v>
-      </c>
       <c r="AA60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
       </c>
       <c r="AC60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
       </c>
       <c r="AE60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AF60" s="3">
         <v>600</v>
       </c>
       <c r="AG60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AH60" s="3">
         <v>700</v>
@@ -5784,13 +5924,16 @@
         <v>700</v>
       </c>
       <c r="AJ60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK60" s="3">
         <v>400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5837,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>100</v>
@@ -5846,7 +5989,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V61" s="3">
         <v>200</v>
@@ -5882,7 +6025,7 @@
         <v>200</v>
       </c>
       <c r="AG61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AH61" s="3">
         <v>300</v>
@@ -5894,10 +6037,13 @@
         <v>300</v>
       </c>
       <c r="AK61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,8 +6071,8 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5956,16 +6102,16 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>2800</v>
       </c>
       <c r="Z62" s="3">
         <v>2800</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>2800</v>
       </c>
+      <c r="AL62" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,13 +6479,16 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
@@ -6372,7 +6530,7 @@
         <v>100</v>
       </c>
       <c r="R66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S66" s="3">
         <v>300</v>
@@ -6381,43 +6539,43 @@
         <v>300</v>
       </c>
       <c r="U66" s="3">
+        <v>300</v>
+      </c>
+      <c r="V66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3200</v>
-      </c>
-      <c r="W66" s="3">
-        <v>3400</v>
       </c>
       <c r="X66" s="3">
         <v>3400</v>
       </c>
       <c r="Y66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3100</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>3400</v>
       </c>
       <c r="AD66" s="3">
         <v>3400</v>
       </c>
       <c r="AE66" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="AF66" s="3">
         <v>3600</v>
       </c>
       <c r="AG66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AH66" s="3">
         <v>3700</v>
@@ -6426,13 +6584,16 @@
         <v>3700</v>
       </c>
       <c r="AJ66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AK66" s="3">
         <v>3500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,8 +7069,11 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6919,7 +7093,7 @@
         <v>-59100</v>
       </c>
       <c r="I72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="J72" s="3">
         <v>-59000</v>
@@ -6928,7 +7102,7 @@
         <v>-59000</v>
       </c>
       <c r="L72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="M72" s="3">
         <v>-59100</v>
@@ -6937,7 +7111,7 @@
         <v>-59100</v>
       </c>
       <c r="O72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="P72" s="3">
         <v>-59200</v>
@@ -6952,61 +7126,64 @@
         <v>-59200</v>
       </c>
       <c r="T72" s="3">
-        <v>-59300</v>
+        <v>-59200</v>
       </c>
       <c r="U72" s="3">
         <v>-59300</v>
       </c>
       <c r="V72" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="W72" s="3">
         <v>-61500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-61300</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-61200</v>
       </c>
       <c r="Y72" s="3">
         <v>-61200</v>
       </c>
       <c r="Z72" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,8 +7509,11 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7335,7 +7521,7 @@
         <v>4500</v>
       </c>
       <c r="E76" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="F76" s="3">
         <v>4600</v>
@@ -7362,10 +7548,10 @@
         <v>4600</v>
       </c>
       <c r="N76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O76" s="3">
         <v>4500</v>
-      </c>
-      <c r="O76" s="3">
-        <v>4400</v>
       </c>
       <c r="P76" s="3">
         <v>4400</v>
@@ -7374,67 +7560,70 @@
         <v>4400</v>
       </c>
       <c r="R76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S76" s="3">
         <v>4500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2300</v>
-      </c>
-      <c r="X76" s="3">
-        <v>2400</v>
       </c>
       <c r="Y76" s="3">
         <v>2400</v>
       </c>
       <c r="Z76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>4700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>400</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>500</v>
       </c>
       <c r="AE76" s="3">
         <v>500</v>
       </c>
       <c r="AF76" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG76" s="3">
         <v>600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7688,10 +7883,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P81" s="3">
         <v>0</v>
@@ -7703,64 +7898,67 @@
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
-        <v>-100</v>
-      </c>
       <c r="W81" s="3">
         <v>-100</v>
       </c>
       <c r="X81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
       <c r="AA81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AC81" s="3">
         <v>-100</v>
       </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AH81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7855,10 +8054,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -7876,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -7894,19 +8093,22 @@
         <v>100</v>
       </c>
       <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AI83" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK83" s="3">
         <v>700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,13 +8654,16 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>0</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -8455,10 +8672,10 @@
         <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I89" s="3">
         <v>0</v>
@@ -8476,32 +8693,32 @@
         <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
@@ -8509,46 +8726,49 @@
         <v>0</v>
       </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>500</v>
       </c>
-      <c r="Z89" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AB89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-300</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
       <c r="AH89" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AI89" s="3">
         <v>400</v>
       </c>
       <c r="AJ89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,16 +8806,17 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
@@ -8603,11 +8824,11 @@
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
@@ -8615,8 +8836,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8645,23 +8866,23 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>8</v>
@@ -8675,8 +8896,8 @@
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
@@ -8688,13 +8909,16 @@
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,16 +9134,19 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
@@ -8924,35 +9154,35 @@
       <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>100</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
@@ -8960,11 +9190,11 @@
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
@@ -8972,24 +9202,24 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AA94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -9009,13 +9239,16 @@
         <v>0</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9510,8 +9756,8 @@
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9526,23 +9772,23 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -9559,22 +9805,22 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>4400</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH100" s="3">
         <v>0</v>
@@ -9583,13 +9829,16 @@
         <v>0</v>
       </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9704,16 +9956,16 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>
@@ -9731,10 +9983,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
@@ -9743,11 +9995,11 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -9764,25 +10016,25 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
-        <v>100</v>
-      </c>
       <c r="AB102" s="3">
         <v>100</v>
       </c>
       <c r="AC102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF102" s="3">
         <v>0</v>
@@ -9791,15 +10043,18 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -843,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -885,16 +889,16 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>100</v>
-      </c>
       <c r="AD8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE8" s="3">
         <v>200</v>
@@ -909,19 +913,22 @@
         <v>200</v>
       </c>
       <c r="AI8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,8 +959,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>8</v>
@@ -982,17 +989,17 @@
       <c r="V9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W9" s="3">
-        <v>200</v>
+      <c r="W9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X9" s="3">
         <v>200</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
         <v>200</v>
@@ -1001,16 +1008,16 @@
         <v>200</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
         <v>200</v>
       </c>
       <c r="AF9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG9" s="3">
         <v>300</v>
@@ -1019,19 +1026,22 @@
         <v>300</v>
       </c>
       <c r="AI9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,8 +1072,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>8</v>
@@ -1092,23 +1102,23 @@
       <c r="V10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W10" s="3">
-        <v>-200</v>
+      <c r="W10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X10" s="3">
         <v>-200</v>
       </c>
       <c r="Y10" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-200</v>
       </c>
-      <c r="AA10" s="3">
-        <v>-100</v>
-      </c>
       <c r="AB10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC10" s="3">
         <v>0</v>
@@ -1120,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="AF10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="3">
         <v>-100</v>
@@ -1135,13 +1145,16 @@
         <v>-100</v>
       </c>
       <c r="AK10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL10" s="3">
         <v>-400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1450,8 +1470,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1468,23 +1488,23 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>2300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1492,26 +1512,29 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-900</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1732,43 +1759,46 @@
         <v>100</v>
       </c>
       <c r="AA17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD17" s="3">
         <v>200</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>300</v>
       </c>
       <c r="AE17" s="3">
         <v>300</v>
       </c>
       <c r="AF17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1797,7 +1827,7 @@
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -1806,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3">
         <v>-100</v>
@@ -1842,11 +1872,11 @@
         <v>-100</v>
       </c>
       <c r="AA18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AB18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AC18" s="3">
         <v>-100</v>
       </c>
@@ -1857,28 +1887,31 @@
         <v>-100</v>
       </c>
       <c r="AF18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,19 +1950,20 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -1949,18 +1983,18 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
@@ -1968,20 +2002,20 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
-        <v>100</v>
-      </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
@@ -1992,16 +2026,16 @@
         <v>100</v>
       </c>
       <c r="AA20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -2010,25 +2044,28 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
       <c r="AK20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AL20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2042,22 +2079,22 @@
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <v>-100</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -2066,34 +2103,34 @@
         <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y21" s="3">
         <v>0</v>
@@ -2102,43 +2139,46 @@
         <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>200</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
       <c r="AD21" s="3">
         <v>0</v>
       </c>
       <c r="AE21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="3">
         <v>-100</v>
       </c>
       <c r="AG21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH21" s="3">
-        <v>0</v>
-      </c>
       <c r="AI21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="3">
         <v>700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,8 +2287,11 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2286,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="3">
         <v>0</v>
@@ -2301,19 +2344,19 @@
         <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y23" s="3">
         <v>0</v>
@@ -2322,43 +2365,46 @@
         <v>0</v>
       </c>
       <c r="AA23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
         <v>100</v>
       </c>
       <c r="AC23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD23" s="3">
         <v>-100</v>
       </c>
       <c r="AE23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH23" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-200</v>
       </c>
-      <c r="AK23" s="3">
-        <v>0</v>
-      </c>
       <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2616,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
@@ -2631,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y26" s="3">
         <v>0</v>
@@ -2652,43 +2704,46 @@
         <v>0</v>
       </c>
       <c r="AA26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="3">
         <v>100</v>
       </c>
       <c r="AC26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD26" s="3">
         <v>-100</v>
       </c>
       <c r="AE26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH26" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-200</v>
       </c>
-      <c r="AK26" s="3">
-        <v>0</v>
-      </c>
       <c r="AL26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2726,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
@@ -2741,19 +2796,19 @@
         <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y27" s="3">
         <v>0</v>
@@ -2762,43 +2817,46 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
         <v>100</v>
       </c>
       <c r="AC27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD27" s="3">
         <v>-100</v>
       </c>
       <c r="AE27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH27" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-200</v>
       </c>
-      <c r="AK27" s="3">
-        <v>0</v>
-      </c>
       <c r="AL27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2945,14 +3006,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2967,28 +3028,28 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>2100</v>
       </c>
-      <c r="W29" s="3">
-        <v>-100</v>
-      </c>
       <c r="X29" s="3">
         <v>-100</v>
       </c>
       <c r="Y29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,19 +3304,22 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -3269,18 +3339,18 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>-100</v>
-      </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
@@ -3288,20 +3358,20 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
-        <v>-100</v>
-      </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
@@ -3312,16 +3382,16 @@
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -3330,25 +3400,28 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AI32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
       <c r="AK32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3386,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="3">
         <v>0</v>
@@ -3401,64 +3474,67 @@
         <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
-        <v>-100</v>
-      </c>
       <c r="X33" s="3">
         <v>-100</v>
       </c>
       <c r="Y33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD33" s="3">
         <v>-100</v>
       </c>
       <c r="AE33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-200</v>
       </c>
-      <c r="AK33" s="3">
-        <v>0</v>
-      </c>
       <c r="AL33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3606,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
@@ -3621,179 +3700,185 @@
         <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
-        <v>-100</v>
-      </c>
       <c r="X35" s="3">
         <v>-100</v>
       </c>
       <c r="Y35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD35" s="3">
         <v>-100</v>
       </c>
       <c r="AE35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-200</v>
       </c>
-      <c r="AK35" s="3">
-        <v>0</v>
-      </c>
       <c r="AL35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,16 +3958,17 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>400</v>
       </c>
       <c r="F41" s="3">
         <v>400</v>
@@ -3896,10 +3983,10 @@
         <v>400</v>
       </c>
       <c r="J41" s="3">
+        <v>400</v>
+      </c>
+      <c r="K41" s="3">
         <v>500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>400</v>
       </c>
       <c r="L41" s="3">
         <v>400</v>
@@ -3914,20 +4001,20 @@
         <v>400</v>
       </c>
       <c r="P41" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q41" s="3">
         <v>300</v>
       </c>
       <c r="R41" s="3">
+        <v>300</v>
+      </c>
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
@@ -3947,22 +4034,22 @@
         <v>0</v>
       </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>400</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>300</v>
       </c>
       <c r="AE41" s="3">
         <v>300</v>
       </c>
       <c r="AF41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG41" s="3">
         <v>400</v>
@@ -3974,16 +4061,19 @@
         <v>400</v>
       </c>
       <c r="AJ41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK41" s="3">
         <v>500</v>
       </c>
-      <c r="AK41" s="3">
-        <v>100</v>
-      </c>
       <c r="AL41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM41" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,8 +4182,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4118,8 +4211,8 @@
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
-        <v>3500</v>
+      <c r="K43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L43" s="3">
         <v>3500</v>
@@ -4134,7 +4227,7 @@
         <v>3500</v>
       </c>
       <c r="P43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="Q43" s="3">
         <v>3600</v>
@@ -4143,46 +4236,46 @@
         <v>3600</v>
       </c>
       <c r="S43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4200</v>
       </c>
-      <c r="AC43" s="3">
-        <v>100</v>
-      </c>
       <c r="AD43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
       <c r="AF43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG43" s="3">
         <v>100</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>100</v>
       </c>
+      <c r="AM43" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,16 +4408,19 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -4330,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -4342,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4366,16 +4465,16 @@
         <v>0</v>
       </c>
       <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
-        <v>100</v>
-      </c>
       <c r="V45" s="3">
         <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
@@ -4393,13 +4492,13 @@
         <v>0</v>
       </c>
       <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>4100</v>
       </c>
-      <c r="AD45" s="3">
-        <v>100</v>
-      </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
@@ -4408,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="AH45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3">
         <v>100</v>
@@ -4417,13 +4516,16 @@
         <v>100</v>
       </c>
       <c r="AK45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL45" s="3">
         <v>200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4434,7 +4536,7 @@
         <v>400</v>
       </c>
       <c r="F46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G46" s="3">
         <v>500</v>
@@ -4449,7 +4551,7 @@
         <v>500</v>
       </c>
       <c r="K46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="L46" s="3">
         <v>4000</v>
@@ -4464,22 +4566,22 @@
         <v>4000</v>
       </c>
       <c r="P46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q46" s="3">
         <v>3900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3900</v>
-      </c>
-      <c r="U46" s="3">
-        <v>3800</v>
       </c>
       <c r="V46" s="3">
         <v>3800</v>
@@ -4488,52 +4590,55 @@
         <v>3800</v>
       </c>
       <c r="X46" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="Y46" s="3">
         <v>4100</v>
       </c>
       <c r="Z46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA46" s="3">
         <v>4300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4500</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>400</v>
       </c>
       <c r="AE46" s="3">
         <v>400</v>
       </c>
       <c r="AF46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AG46" s="3">
         <v>500</v>
       </c>
       <c r="AH46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI46" s="3">
         <v>600</v>
-      </c>
-      <c r="AI46" s="3">
-        <v>700</v>
       </c>
       <c r="AJ46" s="3">
         <v>700</v>
       </c>
       <c r="AK46" s="3">
+        <v>700</v>
+      </c>
+      <c r="AL46" s="3">
         <v>400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4576,8 +4681,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4642,8 +4747,11 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4693,7 +4801,7 @@
         <v>600</v>
       </c>
       <c r="S48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T48" s="3">
         <v>700</v>
@@ -4705,7 +4813,7 @@
         <v>700</v>
       </c>
       <c r="W48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="X48" s="3">
         <v>1400</v>
@@ -4714,46 +4822,49 @@
         <v>1400</v>
       </c>
       <c r="Z48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>3100</v>
       </c>
       <c r="AC48" s="3">
         <v>3100</v>
       </c>
       <c r="AD48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3200</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>3300</v>
       </c>
       <c r="AF48" s="3">
         <v>3300</v>
       </c>
       <c r="AG48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AH48" s="3">
         <v>3400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6200</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>6300</v>
       </c>
       <c r="AK48" s="3">
         <v>6300</v>
       </c>
       <c r="AL48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AM48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5091,10 +5211,10 @@
         <v>3500</v>
       </c>
       <c r="E52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3500</v>
       </c>
       <c r="G52" s="3">
         <v>3500</v>
@@ -5108,14 +5228,14 @@
       <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
+      <c r="K52" s="3">
+        <v>3500</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5133,13 +5253,13 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
@@ -5151,10 +5271,10 @@
         <v>200</v>
       </c>
       <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>200</v>
       </c>
       <c r="AA52" s="3">
         <v>200</v>
@@ -5163,7 +5283,7 @@
         <v>200</v>
       </c>
       <c r="AC52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD52" s="3">
         <v>300</v>
@@ -5187,13 +5307,16 @@
         <v>300</v>
       </c>
       <c r="AK52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL52" s="3">
         <v>400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,8 +5425,11 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5326,16 +5452,16 @@
         <v>4600</v>
       </c>
       <c r="J54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K54" s="3">
         <v>4700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>4600</v>
       </c>
       <c r="N54" s="3">
         <v>4600</v>
@@ -5344,7 +5470,7 @@
         <v>4600</v>
       </c>
       <c r="P54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="Q54" s="3">
         <v>4500</v>
@@ -5353,67 +5479,70 @@
         <v>4500</v>
       </c>
       <c r="S54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="T54" s="3">
         <v>4800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4700</v>
-      </c>
-      <c r="U54" s="3">
-        <v>4600</v>
       </c>
       <c r="V54" s="3">
         <v>4600</v>
       </c>
       <c r="W54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X54" s="3">
         <v>5400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,8 +5622,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5522,10 +5653,10 @@
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5534,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -5555,20 +5686,20 @@
         <v>0</v>
       </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
-        <v>100</v>
-      </c>
       <c r="AB57" s="3">
         <v>100</v>
       </c>
@@ -5576,34 +5707,37 @@
         <v>100</v>
       </c>
       <c r="AD57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5653,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
@@ -5662,7 +5796,7 @@
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5674,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
@@ -5710,10 +5844,13 @@
         <v>100</v>
       </c>
       <c r="AL58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5744,8 +5881,8 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5760,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
@@ -5775,13 +5912,13 @@
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -5802,19 +5939,19 @@
         <v>0</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK59" s="3">
         <v>100</v>
@@ -5822,16 +5959,19 @@
       <c r="AL59" s="3">
         <v>100</v>
       </c>
+      <c r="AM59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
@@ -5873,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="S60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>200</v>
@@ -5882,43 +6022,43 @@
         <v>200</v>
       </c>
       <c r="V60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W60" s="3">
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
         <v>300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3">
-        <v>100</v>
-      </c>
       <c r="AB60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC60" s="3">
         <v>200</v>
       </c>
       <c r="AD60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AE60" s="3">
         <v>400</v>
       </c>
       <c r="AF60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AG60" s="3">
         <v>600</v>
       </c>
       <c r="AH60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AI60" s="3">
         <v>700</v>
@@ -5927,13 +6067,16 @@
         <v>700</v>
       </c>
       <c r="AK60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AL60" s="3">
         <v>400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5983,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -5992,7 +6135,7 @@
         <v>100</v>
       </c>
       <c r="V61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W61" s="3">
         <v>200</v>
@@ -6028,7 +6171,7 @@
         <v>200</v>
       </c>
       <c r="AH61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AI61" s="3">
         <v>300</v>
@@ -6040,10 +6183,13 @@
         <v>300</v>
       </c>
       <c r="AL61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,8 +6220,8 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -6105,16 +6251,16 @@
         <v>0</v>
       </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>2800</v>
       </c>
       <c r="AA62" s="3">
         <v>2800</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>2800</v>
       </c>
+      <c r="AM62" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,16 +6637,19 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F66" s="3">
         <v>100</v>
@@ -6533,7 +6691,7 @@
         <v>100</v>
       </c>
       <c r="S66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T66" s="3">
         <v>300</v>
@@ -6542,43 +6700,43 @@
         <v>300</v>
       </c>
       <c r="V66" s="3">
+        <v>300</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3200</v>
-      </c>
-      <c r="X66" s="3">
-        <v>3400</v>
       </c>
       <c r="Y66" s="3">
         <v>3400</v>
       </c>
       <c r="Z66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AA66" s="3">
         <v>3600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3100</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>3400</v>
       </c>
       <c r="AE66" s="3">
         <v>3400</v>
       </c>
       <c r="AF66" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="AG66" s="3">
         <v>3600</v>
       </c>
       <c r="AH66" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="AI66" s="3">
         <v>3700</v>
@@ -6587,13 +6745,16 @@
         <v>3700</v>
       </c>
       <c r="AK66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AL66" s="3">
         <v>3500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,8 +7243,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7096,7 +7270,7 @@
         <v>-59100</v>
       </c>
       <c r="J72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="K72" s="3">
         <v>-59000</v>
@@ -7105,7 +7279,7 @@
         <v>-59000</v>
       </c>
       <c r="M72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="N72" s="3">
         <v>-59100</v>
@@ -7114,7 +7288,7 @@
         <v>-59100</v>
       </c>
       <c r="P72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="Q72" s="3">
         <v>-59200</v>
@@ -7129,61 +7303,64 @@
         <v>-59200</v>
       </c>
       <c r="U72" s="3">
-        <v>-59300</v>
+        <v>-59200</v>
       </c>
       <c r="V72" s="3">
         <v>-59300</v>
       </c>
       <c r="W72" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="X72" s="3">
         <v>-61500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-61300</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-61200</v>
       </c>
       <c r="Z72" s="3">
         <v>-61200</v>
       </c>
       <c r="AA72" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,8 +7695,11 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7524,7 +7710,7 @@
         <v>4500</v>
       </c>
       <c r="F76" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="G76" s="3">
         <v>4600</v>
@@ -7551,10 +7737,10 @@
         <v>4600</v>
       </c>
       <c r="O76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P76" s="3">
         <v>4500</v>
-      </c>
-      <c r="P76" s="3">
-        <v>4400</v>
       </c>
       <c r="Q76" s="3">
         <v>4400</v>
@@ -7563,67 +7749,70 @@
         <v>4400</v>
       </c>
       <c r="S76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T76" s="3">
         <v>4500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>2400</v>
       </c>
       <c r="Z76" s="3">
         <v>2400</v>
       </c>
       <c r="AA76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB76" s="3">
         <v>4700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>400</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>500</v>
       </c>
       <c r="AF76" s="3">
         <v>500</v>
       </c>
       <c r="AG76" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH76" s="3">
         <v>600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7886,10 +8081,10 @@
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="3">
         <v>0</v>
@@ -7901,64 +8096,67 @@
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
-        <v>-100</v>
-      </c>
       <c r="X81" s="3">
         <v>-100</v>
       </c>
       <c r="Y81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AD81" s="3">
         <v>-100</v>
       </c>
       <c r="AE81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AI81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-200</v>
       </c>
-      <c r="AK81" s="3">
-        <v>0</v>
-      </c>
       <c r="AL81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8057,10 +8256,10 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -8078,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -8096,19 +8295,22 @@
         <v>100</v>
       </c>
       <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>200</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>100</v>
-      </c>
       <c r="AK83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL83" s="3">
         <v>700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8675,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -8696,32 +8913,32 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
@@ -8729,46 +8946,49 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
-        <v>-100</v>
-      </c>
       <c r="AB89" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AC89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-300</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
       <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
       <c r="AI89" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AJ89" s="3">
         <v>400</v>
       </c>
       <c r="AK89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,19 +9027,20 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>8</v>
@@ -8827,11 +9048,11 @@
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
@@ -8839,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8869,23 +9090,23 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
@@ -8899,8 +9120,8 @@
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
@@ -8912,13 +9133,16 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,19 +9364,22 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>8</v>
@@ -9157,35 +9387,35 @@
       <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
-        <v>100</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
+        <v>100</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
@@ -9193,11 +9423,11 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
@@ -9205,24 +9435,24 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AB94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -9242,13 +9472,16 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9759,8 +10005,8 @@
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9775,23 +10021,23 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -9808,22 +10054,22 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>4400</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI100" s="3">
         <v>0</v>
@@ -9832,13 +10078,16 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9956,19 +10208,19 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
@@ -9986,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -9998,11 +10250,11 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
@@ -10019,25 +10271,25 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>100</v>
-      </c>
       <c r="AC102" s="3">
         <v>100</v>
       </c>
       <c r="AD102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG102" s="3">
         <v>0</v>
@@ -10046,15 +10298,18 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GBR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>GBR</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -857,16 +864,16 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -899,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <v>100</v>
@@ -911,7 +918,7 @@
         <v>200</v>
       </c>
       <c r="AG8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH8" s="3">
         <v>200</v>
@@ -923,19 +930,25 @@
         <v>200</v>
       </c>
       <c r="AK8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AL8" s="3">
         <v>200</v>
       </c>
       <c r="AM8" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="AN8" s="3">
         <v>200</v>
       </c>
+      <c r="AO8" s="3">
+        <v>800</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,11 +985,11 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>8</v>
@@ -1002,56 +1015,62 @@
       <c r="X9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="3">
         <v>200</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>200</v>
       </c>
       <c r="AC9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
         <v>200</v>
       </c>
       <c r="AE9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF9" s="3">
         <v>200</v>
       </c>
       <c r="AG9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH9" s="3">
         <v>200</v>
       </c>
-      <c r="AH9" s="3">
-        <v>300</v>
-      </c>
       <c r="AI9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ9" s="3">
         <v>300</v>
       </c>
       <c r="AK9" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AL9" s="3">
         <v>300</v>
       </c>
       <c r="AM9" s="3">
+        <v>500</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO9" s="3">
         <v>1200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1088,11 +1107,11 @@
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>8</v>
@@ -1118,14 +1137,14 @@
       <c r="X10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>-100</v>
       </c>
       <c r="AB10" s="3">
         <v>-200</v>
@@ -1134,10 +1153,10 @@
         <v>-100</v>
       </c>
       <c r="AD10" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AE10" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF10" s="3">
         <v>0</v>
@@ -1146,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="AH10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="3">
         <v>-100</v>
@@ -1161,13 +1180,19 @@
         <v>-100</v>
       </c>
       <c r="AM10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO10" s="3">
         <v>-400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,11 +1517,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1496,11 +1535,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1514,50 +1553,56 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO14" s="3">
         <v>-900</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1762,10 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1792,43 +1845,49 @@
         <v>100</v>
       </c>
       <c r="AC17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE17" s="3">
         <v>300</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>200</v>
       </c>
       <c r="AF17" s="3">
         <v>300</v>
       </c>
       <c r="AG17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1863,19 +1922,19 @@
         <v>-100</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
       <c r="Q18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>-100</v>
@@ -1908,14 +1967,14 @@
         <v>-100</v>
       </c>
       <c r="AC18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-100</v>
-      </c>
       <c r="AF18" s="3">
         <v>-100</v>
       </c>
@@ -1923,28 +1982,34 @@
         <v>-100</v>
       </c>
       <c r="AH18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM18" s="3">
         <v>-300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,28 +2050,30 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="E20" s="3">
+        <v>-100</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
@@ -2023,32 +2090,32 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
@@ -2057,7 +2124,7 @@
         <v>100</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
@@ -2066,51 +2133,57 @@
         <v>100</v>
       </c>
       <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
       <c r="AI20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
@@ -2122,16 +2195,16 @@
         <v>-100</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
         <v>-100</v>
@@ -2140,85 +2213,91 @@
         <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T21" s="3">
         <v>0</v>
       </c>
       <c r="U21" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="V21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X21" s="3">
         <v>100</v>
       </c>
       <c r="Y21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB21" s="3">
         <v>0</v>
       </c>
       <c r="AC21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
       <c r="AG21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3">
-        <v>-100</v>
-      </c>
       <c r="AL21" s="3">
         <v>0</v>
       </c>
       <c r="AM21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="3">
         <v>700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,11 +2334,11 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2333,8 +2412,14 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2378,13 +2463,13 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -2393,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
@@ -2402,55 +2487,61 @@
         <v>100</v>
       </c>
       <c r="Y23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB23" s="3">
         <v>0</v>
       </c>
       <c r="AC23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AF23" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM23" s="3">
-        <v>0</v>
       </c>
       <c r="AN23" s="3">
         <v>-200</v>
       </c>
+      <c r="AO23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,11 +2578,11 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2565,8 +2656,14 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2778,14 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2726,13 +2829,13 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2741,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2750,55 +2853,61 @@
         <v>100</v>
       </c>
       <c r="Y26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB26" s="3">
         <v>0</v>
       </c>
       <c r="AC26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AF26" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM26" s="3">
-        <v>0</v>
       </c>
       <c r="AN26" s="3">
         <v>-200</v>
       </c>
+      <c r="AO26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2842,13 +2951,13 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2857,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2866,55 +2975,61 @@
         <v>100</v>
       </c>
       <c r="Y27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
       <c r="AC27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AF27" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-200</v>
       </c>
-      <c r="AH27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM27" s="3">
-        <v>0</v>
       </c>
       <c r="AN27" s="3">
         <v>-200</v>
       </c>
+      <c r="AO27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3073,17 +3194,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -3095,31 +3216,31 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,28 +3510,34 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="E32" s="3">
+        <v>100</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
@@ -3415,32 +3554,32 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
@@ -3449,7 +3588,7 @@
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
@@ -3458,43 +3597,49 @@
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
       <c r="AI32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3538,13 +3683,13 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -3553,64 +3698,70 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>100</v>
-      </c>
       <c r="AE33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-200</v>
       </c>
-      <c r="AH33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM33" s="3">
-        <v>0</v>
       </c>
       <c r="AN33" s="3">
         <v>-200</v>
       </c>
+      <c r="AO33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3876,14 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3770,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3785,185 +3942,197 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
       <c r="X35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>100</v>
-      </c>
       <c r="AE35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF35" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-200</v>
       </c>
-      <c r="AH35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM35" s="3">
-        <v>0</v>
       </c>
       <c r="AN35" s="3">
         <v>-200</v>
       </c>
+      <c r="AO35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,8 +4217,10 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -4064,7 +4237,7 @@
         <v>400</v>
       </c>
       <c r="H41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I41" s="3">
         <v>400</v>
@@ -4076,13 +4249,13 @@
         <v>400</v>
       </c>
       <c r="L41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M41" s="3">
         <v>400</v>
       </c>
       <c r="N41" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O41" s="3">
         <v>400</v>
@@ -4094,22 +4267,22 @@
         <v>400</v>
       </c>
       <c r="R41" s="3">
+        <v>400</v>
+      </c>
+      <c r="S41" s="3">
+        <v>400</v>
+      </c>
+      <c r="T41" s="3">
         <v>300</v>
-      </c>
-      <c r="S41" s="3">
-        <v>300</v>
-      </c>
-      <c r="T41" s="3">
-        <v>200</v>
       </c>
       <c r="U41" s="3">
         <v>300</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -4127,25 +4300,25 @@
         <v>0</v>
       </c>
       <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>300</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>400</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>400</v>
       </c>
       <c r="AJ41" s="3">
         <v>400</v>
@@ -4154,16 +4327,22 @@
         <v>400</v>
       </c>
       <c r="AL41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AM41" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AN41" s="3">
         <v>500</v>
       </c>
+      <c r="AO41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP41" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,8 +4457,14 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4310,11 +4495,11 @@
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
-        <v>3500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3500</v>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O43" s="3">
         <v>3500</v>
@@ -4326,16 +4511,16 @@
         <v>3500</v>
       </c>
       <c r="R43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="S43" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="T43" s="3">
         <v>3600</v>
       </c>
       <c r="U43" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="V43" s="3">
         <v>3600</v>
@@ -4350,34 +4535,34 @@
         <v>3700</v>
       </c>
       <c r="Z43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB43" s="3">
         <v>4000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4100</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>4300</v>
       </c>
       <c r="AD43" s="3">
         <v>4200</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
+        <v>4300</v>
       </c>
       <c r="AF43" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="AG43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ43" s="3">
         <v>100</v>
@@ -4394,8 +4579,14 @@
       <c r="AN43" s="3">
         <v>100</v>
       </c>
+      <c r="AO43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP43" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,11 +4623,11 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4510,49 +4701,55 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4570,19 +4767,19 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
-        <v>100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>100</v>
-      </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -4597,57 +4794,63 @@
         <v>0</v>
       </c>
       <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
         <v>4100</v>
       </c>
-      <c r="AF45" s="3">
-        <v>100</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>0</v>
-      </c>
       <c r="AH45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
       <c r="AJ45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL45" s="3">
         <v>100</v>
       </c>
       <c r="AM45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO45" s="3">
         <v>200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E46" s="3">
         <v>400</v>
       </c>
       <c r="F46" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G46" s="3">
         <v>400</v>
       </c>
       <c r="H46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J46" s="3">
         <v>500</v>
@@ -4659,10 +4862,10 @@
         <v>500</v>
       </c>
       <c r="M46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="N46" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="O46" s="3">
         <v>4000</v>
@@ -4674,76 +4877,82 @@
         <v>4000</v>
       </c>
       <c r="R46" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="S46" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="T46" s="3">
         <v>3900</v>
       </c>
       <c r="U46" s="3">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="V46" s="3">
         <v>3900</v>
       </c>
       <c r="W46" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="X46" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="Y46" s="3">
         <v>3800</v>
       </c>
       <c r="Z46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB46" s="3">
         <v>4100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4300</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>4500</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>4700</v>
       </c>
       <c r="AE46" s="3">
         <v>4500</v>
       </c>
       <c r="AF46" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AH46" s="3">
         <v>400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>700</v>
-      </c>
-      <c r="AL46" s="3">
-        <v>700</v>
-      </c>
-      <c r="AM46" s="3">
-        <v>400</v>
       </c>
       <c r="AN46" s="3">
         <v>700</v>
       </c>
+      <c r="AO46" s="3">
+        <v>400</v>
+      </c>
+      <c r="AP46" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4792,11 +5001,11 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4858,8 +5067,14 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4915,10 +5130,10 @@
         <v>600</v>
       </c>
       <c r="U48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W48" s="3">
         <v>700</v>
@@ -4927,55 +5142,61 @@
         <v>700</v>
       </c>
       <c r="Y48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="Z48" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="AA48" s="3">
         <v>1400</v>
       </c>
       <c r="AB48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>3100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>3100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>3200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>3300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>3300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>6100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>6200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>6300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>6300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5090,8 +5311,14 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,28 +5555,34 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E52" s="3">
         <v>3500</v>
       </c>
       <c r="F52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G52" s="3">
         <v>3500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3600</v>
       </c>
       <c r="H52" s="3">
         <v>3500</v>
       </c>
       <c r="I52" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="J52" s="3">
         <v>3500</v>
@@ -5354,17 +5593,17 @@
       <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="M52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -5379,16 +5618,16 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
@@ -5397,22 +5636,22 @@
         <v>200</v>
       </c>
       <c r="AA52" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>200</v>
       </c>
       <c r="AC52" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="AD52" s="3">
         <v>200</v>
       </c>
       <c r="AE52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG52" s="3">
         <v>300</v>
@@ -5433,13 +5672,19 @@
         <v>300</v>
       </c>
       <c r="AM52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO52" s="3">
         <v>400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,8 +5799,14 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5566,7 +5817,7 @@
         <v>4600</v>
       </c>
       <c r="F54" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="G54" s="3">
         <v>4600</v>
@@ -5584,7 +5835,7 @@
         <v>4600</v>
       </c>
       <c r="L54" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="M54" s="3">
         <v>4600</v>
@@ -5596,82 +5847,88 @@
         <v>4600</v>
       </c>
       <c r="P54" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="Q54" s="3">
         <v>4600</v>
       </c>
       <c r="R54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="S54" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="T54" s="3">
         <v>4500</v>
       </c>
       <c r="U54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="V54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="W54" s="3">
         <v>4800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>6000</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>8100</v>
       </c>
       <c r="AE54" s="3">
         <v>7900</v>
       </c>
       <c r="AF54" s="3">
+        <v>8100</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AH54" s="3">
         <v>3800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>4100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>7000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>7100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>7300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>7200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,8 +6013,10 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5790,25 +6051,25 @@
         <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -5823,55 +6084,61 @@
         <v>0</v>
       </c>
       <c r="Y57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
       </c>
       <c r="AB57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>100</v>
-      </c>
       <c r="AE57" s="3">
         <v>100</v>
       </c>
       <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>300</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>500</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>400</v>
       </c>
       <c r="AJ57" s="3">
         <v>500</v>
       </c>
       <c r="AK57" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AL57" s="3">
         <v>500</v>
       </c>
       <c r="AM57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO57" s="3">
         <v>200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5927,19 +6194,19 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>100</v>
       </c>
       <c r="X58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5948,10 +6215,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
@@ -5984,10 +6251,16 @@
         <v>100</v>
       </c>
       <c r="AN58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP58" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6024,11 +6297,11 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -6040,10 +6313,10 @@
         <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
@@ -6055,7 +6328,7 @@
         <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
@@ -6064,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -6082,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="AH59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3">
         <v>0</v>
@@ -6097,13 +6370,19 @@
         <v>100</v>
       </c>
       <c r="AM59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN59" s="3">
         <v>100</v>
       </c>
+      <c r="AO59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP59" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -6114,13 +6393,13 @@
         <v>100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>100</v>
       </c>
       <c r="H60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I60" s="3">
         <v>100</v>
@@ -6159,67 +6438,73 @@
         <v>100</v>
       </c>
       <c r="U60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z60" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA60" s="3">
         <v>300</v>
       </c>
       <c r="AB60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF60" s="3">
         <v>200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ60" s="3">
-        <v>700</v>
-      </c>
-      <c r="AK60" s="3">
-        <v>700</v>
       </c>
       <c r="AL60" s="3">
         <v>700</v>
       </c>
       <c r="AM60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AN60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AO60" s="3">
         <v>400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6275,19 +6560,19 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>100</v>
       </c>
       <c r="X61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z61" s="3">
         <v>200</v>
@@ -6320,10 +6605,10 @@
         <v>200</v>
       </c>
       <c r="AJ61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AK61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AL61" s="3">
         <v>300</v>
@@ -6332,10 +6617,16 @@
         <v>300</v>
       </c>
       <c r="AN61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AP61" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,11 +6663,11 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -6403,19 +6694,19 @@
         <v>0</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>2900</v>
       </c>
       <c r="AB62" s="3">
         <v>2800</v>
       </c>
       <c r="AC62" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="AD62" s="3">
         <v>2800</v>
@@ -6450,8 +6741,14 @@
       <c r="AN62" s="3">
         <v>2800</v>
       </c>
+      <c r="AO62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AP62" s="3">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,8 +7107,14 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6810,13 +7125,13 @@
         <v>100</v>
       </c>
       <c r="F66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3">
         <v>100</v>
@@ -6855,67 +7170,73 @@
         <v>100</v>
       </c>
       <c r="U66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>3200</v>
       </c>
       <c r="AE66" s="3">
         <v>3100</v>
       </c>
       <c r="AF66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH66" s="3">
         <v>3400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>3400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>3600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>3600</v>
-      </c>
-      <c r="AJ66" s="3">
-        <v>3700</v>
-      </c>
-      <c r="AK66" s="3">
-        <v>3700</v>
       </c>
       <c r="AL66" s="3">
         <v>3700</v>
       </c>
       <c r="AM66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AN66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AO66" s="3">
         <v>3500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,8 +7761,14 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7432,7 +7779,7 @@
         <v>-59100</v>
       </c>
       <c r="F72" s="3">
-        <v>-59100</v>
+        <v>-59200</v>
       </c>
       <c r="G72" s="3">
         <v>-59100</v>
@@ -7450,28 +7797,28 @@
         <v>-59100</v>
       </c>
       <c r="L72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="M72" s="3">
-        <v>-59000</v>
+        <v>-59100</v>
       </c>
       <c r="N72" s="3">
         <v>-59000</v>
       </c>
       <c r="O72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="P72" s="3">
-        <v>-59100</v>
+        <v>-59000</v>
       </c>
       <c r="Q72" s="3">
         <v>-59100</v>
       </c>
       <c r="R72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="S72" s="3">
-        <v>-59200</v>
+        <v>-59100</v>
       </c>
       <c r="T72" s="3">
         <v>-59200</v>
@@ -7483,61 +7830,67 @@
         <v>-59200</v>
       </c>
       <c r="W72" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="X72" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-59300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-59300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-61300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-61200</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>-58900</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-58700</v>
       </c>
       <c r="AE72" s="3">
         <v>-58900</v>
       </c>
       <c r="AF72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-58800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-58500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-58400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-55500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-55400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-55300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-55100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-55800</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,8 +8249,14 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7902,10 +8273,10 @@
         <v>4500</v>
       </c>
       <c r="H76" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="I76" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="J76" s="3">
         <v>4600</v>
@@ -7929,79 +8300,85 @@
         <v>4600</v>
       </c>
       <c r="Q76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="R76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S76" s="3">
         <v>4500</v>
-      </c>
-      <c r="R76" s="3">
-        <v>4400</v>
-      </c>
-      <c r="S76" s="3">
-        <v>4400</v>
       </c>
       <c r="T76" s="3">
         <v>4400</v>
       </c>
       <c r="U76" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="V76" s="3">
         <v>4400</v>
       </c>
       <c r="W76" s="3">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="X76" s="3">
         <v>4400</v>
       </c>
       <c r="Y76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>3300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>3400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>3600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>3700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8493,141 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8282,13 +8671,13 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -8297,64 +8686,70 @@
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
       <c r="X81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-100</v>
-      </c>
       <c r="AA81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>100</v>
-      </c>
       <c r="AE81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-200</v>
       </c>
-      <c r="AH81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-300</v>
-      </c>
-      <c r="AL81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AM81" s="3">
-        <v>0</v>
       </c>
       <c r="AN81" s="3">
         <v>-200</v>
       </c>
+      <c r="AO81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8790,10 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8461,13 +8858,13 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -8482,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
@@ -8500,19 +8897,25 @@
         <v>100</v>
       </c>
       <c r="AK83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM83" s="3">
         <v>200</v>
       </c>
-      <c r="AL83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO83" s="3">
         <v>700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,16 +9518,22 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F89" s="3">
         <v>0</v>
@@ -9115,13 +9548,13 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -9136,79 +9569,85 @@
         <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
       <c r="S89" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
       <c r="U89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>100</v>
-      </c>
       <c r="AE89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-300</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="3">
         <v>400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9688,10 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9263,35 +9704,35 @@
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9317,26 +9758,26 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
+      <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
@@ -9347,11 +9788,11 @@
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK91" s="3">
         <v>0</v>
@@ -9360,13 +9801,19 @@
         <v>0</v>
       </c>
       <c r="AM91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,8 +10050,14 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9611,87 +10070,87 @@
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S94" s="3">
-        <v>100</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
+      <c r="U94" s="3">
+        <v>100</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
@@ -9708,13 +10167,19 @@
         <v>0</v>
       </c>
       <c r="AM94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
         <v>700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10260,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,8 +10704,14 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10257,11 +10748,11 @@
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -10273,26 +10764,26 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -10306,37 +10797,43 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>4400</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>200</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
       <c r="AK100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL100" s="3">
         <v>0</v>
       </c>
       <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,11 +10870,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10451,37 +10948,43 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -10496,26 +10999,26 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
@@ -10529,42 +11032,48 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE102" s="3">
-        <v>100</v>
-      </c>
       <c r="AF102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AH102" s="3">
         <v>0</v>
       </c>
       <c r="AI102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ102" s="3">
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>100</v>
       </c>
     </row>
